--- a/long_peptide/annotation_protein.xlsx
+++ b/long_peptide/annotation_protein.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevinmbp/Desktop/2D_spec_dict/long_peptide/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6176A7-E994-214F-AF31-1CD2B31DD719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB299CD-CDE6-6A4E-8E95-B03B0B51835A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="51580" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="51580" windowHeight="23520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEADIAGHGQEVLIR3+" sheetId="1" r:id="rId1"/>
     <sheet name="YLEFISDAIIHVLHSK3+" sheetId="4" r:id="rId2"/>
     <sheet name="HGTVVLTALGGILK3+" sheetId="5" r:id="rId3"/>
     <sheet name="HADGSFSDEMNTILDNLAARDFINWLIQT4+" sheetId="2" r:id="rId4"/>
-    <sheet name="protein" sheetId="3" r:id="rId5"/>
+    <sheet name="protein" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="1214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="1350">
   <si>
     <t>N=800</t>
   </si>
@@ -1229,27 +1229,6 @@
     <t>0, +2, [1, 18], (0.004, 0.029), [3489]</t>
   </si>
   <si>
-    <t>0, +3, [1, 18], (0.004, 0.058), [696]</t>
-  </si>
-  <si>
-    <t>0, +6, [1, 18], (0.004, 0.018), [369]</t>
-  </si>
-  <si>
-    <t>0, +9, [1, 18], (0.004, 0.01), [49]</t>
-  </si>
-  <si>
-    <t>0, +10, [1, 18], (0.004, 0.008), [2]</t>
-  </si>
-  <si>
-    <t>+1, +10, [1, 18], (0.003, 0.008), [294]</t>
-  </si>
-  <si>
-    <t>+1, +11, [1, 18], (0.003, 0.014), [562]</t>
-  </si>
-  <si>
-    <t>0, +13, [1, 18], (0.004, 0.008), [92]</t>
-  </si>
-  <si>
     <t>(745.315, 16197.664)</t>
   </si>
   <si>
@@ -1265,12 +1244,6 @@
     <t>+11, +3, [1, 17], (0.008, 0.067), [1451]</t>
   </si>
   <si>
-    <t>+3, +13, [1, 17], (0.021, 0.032), [9508]</t>
-  </si>
-  <si>
-    <t>+2, ???, [1, 18], (0.013, 'n/a'), [4768]</t>
-  </si>
-  <si>
     <t>(873.374, 16069.605)</t>
   </si>
   <si>
@@ -1283,12 +1256,6 @@
     <t>b10, y143</t>
   </si>
   <si>
-    <t>(7, 9)</t>
-  </si>
-  <si>
-    <t>+7, +9, [1, 18], (0.021, 0.022), [768]</t>
-  </si>
-  <si>
     <t>(1100.501, 15842.478)</t>
   </si>
   <si>
@@ -1355,27 +1322,6 @@
     <t>b20, y133</t>
   </si>
   <si>
-    <t>(1, 4)</t>
-  </si>
-  <si>
-    <t>+1, +4, [2, 17], (0.009, 0.033), [9781]</t>
-  </si>
-  <si>
-    <t>+2, +4, [2, 17], (0.009, 0.033), [24]</t>
-  </si>
-  <si>
-    <t>0, +7, [2, 17], (0.01, 0.012), [1865]</t>
-  </si>
-  <si>
-    <t>0, +8, [2, 17], (0.01, 0.029), [716]</t>
-  </si>
-  <si>
-    <t>+2, +7, [2, 17], (0.009, 0.012), [182]</t>
-  </si>
-  <si>
-    <t>+2, +8, [2, 17], (0.009, 0.029), [3143]</t>
-  </si>
-  <si>
     <t>(2212.067, 14730.912)</t>
   </si>
   <si>
@@ -1484,27 +1430,9 @@
     <t>b36, y117</t>
   </si>
   <si>
-    <t>(0, 7)</t>
-  </si>
-  <si>
-    <t>0, +7, [4, 15], (0.012, 0.044), [1682]</t>
-  </si>
-  <si>
-    <t>+1, +7, [4, 15], (0.016, 0.044), [1384]</t>
-  </si>
-  <si>
     <t>+3, +6, [4, 15], (0.015, 0.05), [4920]</t>
   </si>
   <si>
-    <t>+2, +8, [4, 15], (0.017, 0.039), [126]</t>
-  </si>
-  <si>
-    <t>0, +11, [4, 15], (0.012, 0.04), [2897]</t>
-  </si>
-  <si>
-    <t>+1, +12, [4, 15], (0.016, 0.027), [16]</t>
-  </si>
-  <si>
     <t>(3941.009, 13001.97)</t>
   </si>
   <si>
@@ -1565,18 +1493,6 @@
     <t>(3, 5)</t>
   </si>
   <si>
-    <t>+3, +5, [5, 14], (0.025, 0.038), [3607]</t>
-  </si>
-  <si>
-    <t>+3, +6, [5, 14], (0.025, 0.029), [2557]</t>
-  </si>
-  <si>
-    <t>+4, +6, [5, 14], (0.017, 0.029), [8214]</t>
-  </si>
-  <si>
-    <t>+2, +9, [5, 14], (0.034, 0.017), [4719]</t>
-  </si>
-  <si>
     <t>(4900.469, 12042.51)</t>
   </si>
   <si>
@@ -1595,15 +1511,6 @@
     <t>b47, y106</t>
   </si>
   <si>
-    <t>(3, 3)</t>
-  </si>
-  <si>
-    <t>+3, +3, [6, 13], (0.029, 0.001), [8283]</t>
-  </si>
-  <si>
-    <t>+3, +4, [6, 13], (0.029, 0.009), [1520]</t>
-  </si>
-  <si>
     <t>+2, +11, [6, 13], (0.034, 0.062), [4844]</t>
   </si>
   <si>
@@ -1643,12 +1550,6 @@
     <t>b52, y101</t>
   </si>
   <si>
-    <t>(5, 6)</t>
-  </si>
-  <si>
-    <t>+5, +6, [6, 13], (0.009, 0.055), [1300]</t>
-  </si>
-  <si>
     <t>(5912.056, 11030.923)</t>
   </si>
   <si>
@@ -1661,36 +1562,9 @@
     <t>b54, y99</t>
   </si>
   <si>
-    <t>+2, +3, [6, 13], (0.021, 0.033), [1323]</t>
-  </si>
-  <si>
-    <t>+3, +3, [6, 13], (0.022, 0.033), [2773]</t>
-  </si>
-  <si>
-    <t>+3, +4, [6, 13], (0.022, 0.032), [9262]</t>
-  </si>
-  <si>
     <t>+4, +4, [7, 12], (0.038, 0.02), [5828]</t>
   </si>
   <si>
-    <t>+1, +8, [6, 13], (0.021, 0.029), [1385]</t>
-  </si>
-  <si>
-    <t>+1, +9, [6, 13], (0.021, 0.022), [8732]</t>
-  </si>
-  <si>
-    <t>+5, +6, [6, 13], (0.018, 0.03), [174]</t>
-  </si>
-  <si>
-    <t>+2, +10, [6, 13], (0.021, 0.005), [4277]</t>
-  </si>
-  <si>
-    <t>+4, +9, [6, 13], (0.02, 0.022), [1050]</t>
-  </si>
-  <si>
-    <t>+4, +10, [6, 13], (0.02, 0.005), [865]</t>
-  </si>
-  <si>
     <t>+9, +6, [7, 12], (0.028, 0.003), [3868]</t>
   </si>
   <si>
@@ -1715,9 +1589,6 @@
     <t>(5, 2)</t>
   </si>
   <si>
-    <t>+5, +2, [7, 12], (0.09, 0.072), [2075]</t>
-  </si>
-  <si>
     <t>(6371.271, 10571.708)</t>
   </si>
   <si>
@@ -1745,30 +1616,6 @@
     <t>b60, y93</t>
   </si>
   <si>
-    <t>+3, +3, [7, 12], (0.025, 0.026), [4972]</t>
-  </si>
-  <si>
-    <t>+4, +3, [7, 12], (0.025, 0.026), [721]</t>
-  </si>
-  <si>
-    <t>+3, +5, [7, 12], (0.025, 0.029), [3382]</t>
-  </si>
-  <si>
-    <t>+4, +5, [7, 12], (0.025, 0.029), [23]</t>
-  </si>
-  <si>
-    <t>+5, +5, [7, 12], (0.017, 0.029), [3797]</t>
-  </si>
-  <si>
-    <t>+2, +9, [7, 12], (0.01, 0.03), [4608]</t>
-  </si>
-  <si>
-    <t>+4, +8, [7, 12], (0.025, 0.019), [8569]</t>
-  </si>
-  <si>
-    <t>+6, +7, [7, 12], (0.016, 0.023), [7841]</t>
-  </si>
-  <si>
     <t>(6773.41, 10169.57)</t>
   </si>
   <si>
@@ -1790,18 +1637,6 @@
     <t>(4, 4)</t>
   </si>
   <si>
-    <t>+4, +4, [7, 12], (0.023, 0.026), [8224]</t>
-  </si>
-  <si>
-    <t>+4, +5, [7, 12], (0.023, 0.027), [1390]</t>
-  </si>
-  <si>
-    <t>+4, +6, [7, 12], (0.023, 0.027), [405]</t>
-  </si>
-  <si>
-    <t>+4, +7, [7, 12], (0.023, 0.028), [495]</t>
-  </si>
-  <si>
     <t>(7142.684, 9800.296)</t>
   </si>
   <si>
@@ -1817,9 +1652,6 @@
     <t>+7, +7, [8, 11], (0.066, 0.012), [985]</t>
   </si>
   <si>
-    <t>+6, +12, [8, 11], (0.049, 0.058), [1411]</t>
-  </si>
-  <si>
     <t>(7279.742, 9663.237)</t>
   </si>
   <si>
@@ -1868,9 +1700,6 @@
     <t>b72, y81</t>
   </si>
   <si>
-    <t>+13, ???, [9, 10], (0.066, 'n/a'), [3964]</t>
-  </si>
-  <si>
     <t>(8034.201, 8908.778)</t>
   </si>
   <si>
@@ -1901,12 +1730,6 @@
     <t>b76, y77</t>
   </si>
   <si>
-    <t>(7, 13)</t>
-  </si>
-  <si>
-    <t>+7, +13, [9, 9], (0.028, 0.044), [198]</t>
-  </si>
-  <si>
     <t>(8374.412, 8568.567)</t>
   </si>
   <si>
@@ -2036,30 +1859,12 @@
     <t>(5, 3)</t>
   </si>
   <si>
-    <t>+5, +3, [11, 8], (0.035, 0.02), [614]</t>
-  </si>
-  <si>
-    <t>+8, +1, [11, 8], (0.027, 0.018), [2047]</t>
-  </si>
-  <si>
-    <t>+8, +2, [11, 8], (0.027, 0.02), [3729]</t>
-  </si>
-  <si>
-    <t>+8, +4, [11, 8], (0.027, 0.019), [1024]</t>
-  </si>
-  <si>
-    <t>+7, +6, [11, 8], (0.026, 0.016), [51]</t>
-  </si>
-  <si>
     <t>(10593.641, 6349.338)</t>
   </si>
   <si>
     <t>b97, y56</t>
   </si>
   <si>
-    <t>(6, 0)</t>
-  </si>
-  <si>
     <t>+6, 0, [12, 7], (0.072, 0.054), [8174]</t>
   </si>
   <si>
@@ -2078,24 +1883,9 @@
     <t>(5, 1)</t>
   </si>
   <si>
-    <t>+5, +1, [12, 7], (0.032, 0.023), [2194]</t>
-  </si>
-  <si>
     <t>+4, +3, [12, 7], (0.036, 0.016), [1478]</t>
   </si>
   <si>
-    <t>+6, +2, [12, 7], (0.032, 0.025), [2347]</t>
-  </si>
-  <si>
-    <t>+6, +3, [12, 7], (0.032, 0.016), [1407]</t>
-  </si>
-  <si>
-    <t>+8, +2, [12, 7], (0.017, 0.025), [4140]</t>
-  </si>
-  <si>
-    <t>+7, +4, [12, 7], (0.002, 0.02), [1746]</t>
-  </si>
-  <si>
     <t>(10971.879, 5971.1)</t>
   </si>
   <si>
@@ -2129,9 +1919,6 @@
     <t>b104, y49</t>
   </si>
   <si>
-    <t>+6, 0, [13, 6], (0.019, 0.07), [3555]</t>
-  </si>
-  <si>
     <t>(11586.258, 5356.721)</t>
   </si>
   <si>
@@ -2144,9 +1931,6 @@
     <t>+6, +3, [13, 6], (0.038, 0.02), [791]</t>
   </si>
   <si>
-    <t>+7, +3, [13, 6], (0.034, 0.02), [2858]</t>
-  </si>
-  <si>
     <t>(11715.301, 5227.678)</t>
   </si>
   <si>
@@ -2159,12 +1943,6 @@
     <t>b107, y46</t>
   </si>
   <si>
-    <t>(2, 1)</t>
-  </si>
-  <si>
-    <t>+2, +1, [13, 6], (0.075, 0.004), [7651]</t>
-  </si>
-  <si>
     <t>+8, +1, [13, 6], (0.071, 0.004), [5968]</t>
   </si>
   <si>
@@ -2189,9 +1967,6 @@
     <t>+5, +3, [13, 6], (0.045, 0.013), [2539]</t>
   </si>
   <si>
-    <t>+6, +3, [13, 6], (0.047, 0.013), [6354]</t>
-  </si>
-  <si>
     <t>(12177.512, 4765.467)</t>
   </si>
   <si>
@@ -2240,15 +2015,6 @@
     <t>b114, y39</t>
   </si>
   <si>
-    <t>+5, +3, [14, 5], (0.034, 0.011), [9468]</t>
-  </si>
-  <si>
-    <t>+7, +2, [14, 5], (0.043, 0.017), [383]</t>
-  </si>
-  <si>
-    <t>+7, +3, [14, 5], (0.043, 0.011), [5517]</t>
-  </si>
-  <si>
     <t>(12710.845, 4232.134)</t>
   </si>
   <si>
@@ -2282,9 +2048,6 @@
     <t>+6, +1, [14, 5], (0.022, 0.012), [4361]</t>
   </si>
   <si>
-    <t>+9, +1, [14, 5], (0.041, 0.012), [9716]</t>
-  </si>
-  <si>
     <t>+11, +1, [14, 5], (0.032, 0.012), [3771]</t>
   </si>
   <si>
@@ -2294,33 +2057,9 @@
     <t>b119, y34</t>
   </si>
   <si>
-    <t>(4, 1)</t>
-  </si>
-  <si>
-    <t>+4, +1, [14, 5], (0.042, 0.012), [1966]</t>
-  </si>
-  <si>
     <t>+5, +2, [14, 5], (0.026, 0.011), [3303]</t>
   </si>
   <si>
-    <t>+8, 0, [14, 5], (0.042, 0.013), [1911]</t>
-  </si>
-  <si>
-    <t>+7, +2, [14, 5], (0.005, 0.011), [5767]</t>
-  </si>
-  <si>
-    <t>+9, +1, [14, 5], (0.015, 0.012), [83]</t>
-  </si>
-  <si>
-    <t>+10, +1, [14, 5], (0.008, 0.012), [7145]</t>
-  </si>
-  <si>
-    <t>+10, +2, [14, 5], (0.008, 0.011), [281]</t>
-  </si>
-  <si>
-    <t>+11, +4, [14, 5], (0.026, 0.008), [377]</t>
-  </si>
-  <si>
     <t>(13313.174, 3629.806)</t>
   </si>
   <si>
@@ -2345,12 +2084,6 @@
     <t>+7, +2, [15, 4], (0.094, 0.013), [6]</t>
   </si>
   <si>
-    <t>+8, +3, [15, 4], (0.018, 0.011), [112]</t>
-  </si>
-  <si>
-    <t>+11, +3, [15, 4], (0.027, 0.011), [4872]</t>
-  </si>
-  <si>
     <t>(13582.275, 3360.704)</t>
   </si>
   <si>
@@ -2393,9 +2126,6 @@
     <t>b129, y24</t>
   </si>
   <si>
-    <t>+4, +4, [16, 3], (0.059, 0.003), [571]</t>
-  </si>
-  <si>
     <t>(14228.546, 2714.433)</t>
   </si>
   <si>
@@ -2441,9 +2171,6 @@
     <t>(8, 1)</t>
   </si>
   <si>
-    <t>+8, +1, [16, 3], (0.053, 0.007), [3438]</t>
-  </si>
-  <si>
     <t>(14972.93, 1970.049)</t>
   </si>
   <si>
@@ -2501,12 +2228,6 @@
     <t>b145, y8</t>
   </si>
   <si>
-    <t>(4, 2)</t>
-  </si>
-  <si>
-    <t>+4, +2, [18, 1], (0.07, 0.039), [9158]</t>
-  </si>
-  <si>
     <t>+3, +5, [18, 1], (0.028, 0.097), [8335]</t>
   </si>
   <si>
@@ -2555,195 +2276,6 @@
     <t>(16866.94, 76.039)</t>
   </si>
   <si>
-    <t>(889.349968, 920.554971, [17, 2], 9884)</t>
-  </si>
-  <si>
-    <t>(901.491135, 950.446606, [3, 15], 9733)</t>
-  </si>
-  <si>
-    <t>(920.328227, 964.345756, [9, 9], 9606)</t>
-  </si>
-  <si>
-    <t>(876.726717, 900.212627, [6, 13], 9779)</t>
-  </si>
-  <si>
-    <t>(941.099553, 965.467389, [17, 1], 9854)</t>
-  </si>
-  <si>
-    <t>(887.32396, 896.954702, [8, 11], 9751)</t>
-  </si>
-  <si>
-    <t>(884.111342, 899.378478, [8, 11], 9883)</t>
-  </si>
-  <si>
-    <t>(890.429223, 900.212627, [14, 5], 9980)</t>
-  </si>
-  <si>
-    <t>(885.134601, 893.985406, [2, 17], 9900)</t>
-  </si>
-  <si>
-    <t>(892.721278, 900.212627, [18, 1], 9680)</t>
-  </si>
-  <si>
-    <t>(887.009654, 964.240179, [5, 13], 9411)</t>
-  </si>
-  <si>
-    <t>(882.006717, 912.440234, [12, 7], 9894)</t>
-  </si>
-  <si>
-    <t>(928.836198, 949.920782, [6, 12], 9836)</t>
-  </si>
-  <si>
-    <t>(882.953862, 922.359924, [14, 5], 9922)</t>
-  </si>
-  <si>
-    <t>(888.563913, 919.055249, [16, 3], 9942)</t>
-  </si>
-  <si>
-    <t>(825.219727, 911.608256, [4, 15], 9846)</t>
-  </si>
-  <si>
-    <t>(891.589207, 927.500786, [18, 1], 9058)</t>
-  </si>
-  <si>
-    <t>(884.427777, 927.668954, [15, 4], 9908)</t>
-  </si>
-  <si>
-    <t>(882.320646, 901.771143, [8, 11], 9881)</t>
-  </si>
-  <si>
-    <t>(883.87291, 910.379885, [12, 7], 9861)</t>
-  </si>
-  <si>
-    <t>+5, ???, [9, 10], (0.073, 'n/a'), [8883]|</t>
-  </si>
-  <si>
-    <t>(878.92329, 911.495458, [11, 8], 9763)</t>
-  </si>
-  <si>
-    <t>(889.880804, 893.694215, [5, 14], 9696)</t>
-  </si>
-  <si>
-    <t>(885.725374, 930.198429, [16, 3], 9563)</t>
-  </si>
-  <si>
-    <t>(891.905201, 893.115737, [5, 14], 9580)</t>
-  </si>
-  <si>
-    <t>(883.216139, 893.377617, [1, 18], 9463)</t>
-  </si>
-  <si>
-    <t>(886.269211, 893.272781, [1, 18], 9240)</t>
-  </si>
-  <si>
-    <t>(849.930166, 931.671067, [9, 10], 9453)</t>
-  </si>
-  <si>
-    <t>(883.742299, 918.943957, [14, 5], 9919)</t>
-  </si>
-  <si>
-    <t>(934.220309, 959.587988, [12, 6], 9831)</t>
-  </si>
-  <si>
-    <t>(872.457723, 900.489713, [5, 14], 9429)</t>
-  </si>
-  <si>
-    <t>(940.488128, 954.226884, [15, 3], 8833)</t>
-  </si>
-  <si>
-    <t>(928.50288, 943.677367, [1, 17], 9571)</t>
-  </si>
-  <si>
-    <t>(880.373052, 921.198617, [13, 6], 9461)</t>
-  </si>
-  <si>
-    <t>(938.511806, 965.172264, [15, 3], 9115)</t>
-  </si>
-  <si>
-    <t>(888.588611, 979.510687, [18, 1], 9759)</t>
-  </si>
-  <si>
-    <t>(890.880495, 907.02815, [16, 3], 9817)</t>
-  </si>
-  <si>
-    <t>(891.090251, 906.246872, [16, 3], 8848)</t>
-  </si>
-  <si>
-    <t>(892.852942, 899.263355, [17, 2], 9787)</t>
-  </si>
-  <si>
-    <t>(879.529359, 932.947954, [14, 5], 9620)</t>
-  </si>
-  <si>
-    <t>???, +11, [16, 3], ('n/a', 0.005), [9738]|</t>
-  </si>
-  <si>
-    <t>(892.326211, 895.558153, [11, 8], 8717)</t>
-  </si>
-  <si>
-    <t>(881.697816, 900.601633, [8, 11], 9050)</t>
-  </si>
-  <si>
-    <t>(890.351754, 912.552326, [17, 2], 9558)</t>
-  </si>
-  <si>
-    <t>(884.058715, 925.311176, [15, 4], 9363)</t>
-  </si>
-  <si>
-    <t>(938.676936, 947.047692, [10, 8], 9391)</t>
-  </si>
-  <si>
-    <t>(889.903749, 945.872042, [18, 1], 9245)</t>
-  </si>
-  <si>
-    <t>(888.878762, 898.427764, [11, 8], 9129)</t>
-  </si>
-  <si>
-    <t>(889.615294, 902.316457, [14, 5], 9224)</t>
-  </si>
-  <si>
-    <t>(917.221925, 952.378823, [5, 13], 8842)</t>
-  </si>
-  <si>
-    <t>(892.484975, 903.433763, [18, 1], 9742)</t>
-  </si>
-  <si>
-    <t>(939.429845, 951.30928, [13, 5], 9284)</t>
-  </si>
-  <si>
-    <t>(887.693281, 908.492604, [14, 5], 8680)</t>
-  </si>
-  <si>
-    <t>(889.955992, 894.376658, [5, 14], 9308)</t>
-  </si>
-  <si>
-    <t>(880.952742, 919.943538, [13, 6], 9114)</t>
-  </si>
-  <si>
-    <t>(892.852942, 893.535915, [6, 13], 9060)</t>
-  </si>
-  <si>
-    <t>(891.746271, 907.239106, [17, 2], 9630)</t>
-  </si>
-  <si>
-    <t>(888.746333, 933.226007, [17, 2], 9310)</t>
-  </si>
-  <si>
-    <t>(892.353036, 983.725849, [8, 10], 8723)</t>
-  </si>
-  <si>
-    <t>(891.37805, 932.33671, [18, 1], 9734)</t>
-  </si>
-  <si>
-    <t>(908.278543, 950.221699, [3, 15], 9591)</t>
-  </si>
-  <si>
-    <t>(881.697816, 900.601633, [7, 12], 9050)</t>
-  </si>
-  <si>
-    <t>(868.209819, 895.108533, [1, 18], 8699)</t>
-  </si>
-  <si>
     <t>All Coverage=87.5%</t>
   </si>
   <si>
@@ -3666,6 +3198,882 @@
   </si>
   <si>
     <t>N=500</t>
+  </si>
+  <si>
+    <t>(6226.2042, 10753.9231, 16980.1273)</t>
+  </si>
+  <si>
+    <t>(14184.5912, 2793.4982, 16978.0895)</t>
+  </si>
+  <si>
+    <t>(11615.2745, 5361.8474, 16977.1218)</t>
+  </si>
+  <si>
+    <t>(15108.2457, 1866.8978, 16975.1436)</t>
+  </si>
+  <si>
+    <t>(2668.4492, 14305.6851, 16974.1342)</t>
+  </si>
+  <si>
+    <t>(12440.6406, 4532.4606, 16973.1012)</t>
+  </si>
+  <si>
+    <t>(3553.9315, 13418.1279, 16972.0594)</t>
+  </si>
+  <si>
+    <t>(5356.797, 11614.3236, 16971.1206)</t>
+  </si>
+  <si>
+    <t>(14198.8823, 2771.1828, 16970.0651)</t>
+  </si>
+  <si>
+    <t>(8797.6129, 8170.452, 16968.0648)</t>
+  </si>
+  <si>
+    <t>(6247.2182, 10719.9037, 16967.1219)</t>
+  </si>
+  <si>
+    <t>(15050.1173, 1915.9911, 16966.1084)</t>
+  </si>
+  <si>
+    <t>(6230.4328, 10734.6595, 16965.0923)</t>
+  </si>
+  <si>
+    <t>(12491.8405, 4470.3031, 16962.1436)</t>
+  </si>
+  <si>
+    <t>(15100.2051, 1860.8918, 16961.0969)</t>
+  </si>
+  <si>
+    <t>TFPR1_LIST_3</t>
+  </si>
+  <si>
+    <t>(885.301, 16094.8506, 16980.1516)</t>
+  </si>
+  <si>
+    <t>(2665.4486, 14312.6698, 16978.1184)</t>
+  </si>
+  <si>
+    <t>(9686.451, 7290.6384, 16977.0894)</t>
+  </si>
+  <si>
+    <t>(892.4317, 16083.6465, 16976.0781)</t>
+  </si>
+  <si>
+    <t>(6245.1808, 10729.9004, 16975.0812)</t>
+  </si>
+  <si>
+    <t>(13191.1076, 3783.009, 16974.1166)</t>
+  </si>
+  <si>
+    <t>(7095.9001, 9877.2364, 16973.1365)</t>
+  </si>
+  <si>
+    <t>(888.4298, 16083.6465, 16972.0763)</t>
+  </si>
+  <si>
+    <t>(11590.3192, 5380.7913, 16971.1105)</t>
+  </si>
+  <si>
+    <t>(12315.6449, 4654.4615, 16970.1065)</t>
+  </si>
+  <si>
+    <t>(5570.0132, 11399.0494, 16969.0625)</t>
+  </si>
+  <si>
+    <t>(12495.8983, 4472.1622, 16968.0605)</t>
+  </si>
+  <si>
+    <t>(12463.8128, 4503.2898, 16967.1026)</t>
+  </si>
+  <si>
+    <t>(5890.0589, 11076.0091, 16966.068)</t>
+  </si>
+  <si>
+    <t>(887.324, 16077.7883, 16965.1123)</t>
+  </si>
+  <si>
+    <t>(9817.3347, 7145.764, 16963.0987)</t>
+  </si>
+  <si>
+    <t>(10577.7666, 6384.3725, 16962.139)</t>
+  </si>
+  <si>
+    <t>(6246.2835, 10714.8674, 16961.1509)</t>
+  </si>
+  <si>
+    <t>TFPR1_LIST_2</t>
+  </si>
+  <si>
+    <t>(8933.7762, 8046.3559, 16980.1321)</t>
+  </si>
+  <si>
+    <t>(10493.5357, 6485.538, 16979.0737)</t>
+  </si>
+  <si>
+    <t>(7464.0299, 9513.0928, 16977.1227)</t>
+  </si>
+  <si>
+    <t>(14198.8823, 2777.1911, 16976.0735)</t>
+  </si>
+  <si>
+    <t>(15173.1108, 1801.985, 16975.0958)</t>
+  </si>
+  <si>
+    <t>(12444.6479, 4529.4296, 16974.0775)</t>
+  </si>
+  <si>
+    <t>(3552.7585, 13420.3643, 16973.1227)</t>
+  </si>
+  <si>
+    <t>(14194.5613, 2777.5778, 16972.1391)</t>
+  </si>
+  <si>
+    <t>(5353.8069, 11617.3359, 16971.1428)</t>
+  </si>
+  <si>
+    <t>(4245.2923, 12724.8223, 16970.1146)</t>
+  </si>
+  <si>
+    <t>(880.2674, 16088.805, 16969.0724)</t>
+  </si>
+  <si>
+    <t>(11609.4355, 5358.6944, 16968.1299)</t>
+  </si>
+  <si>
+    <t>(9625.353, 7341.766, 16967.119)</t>
+  </si>
+  <si>
+    <t>(16023.5024, 942.5666, 16966.069)</t>
+  </si>
+  <si>
+    <t>(15097.0473, 1868.0099, 16965.0572)</t>
+  </si>
+  <si>
+    <t>(15168.2443, 1795.8612, 16964.1055)</t>
+  </si>
+  <si>
+    <t>(1884.0291, 15079.1205, 16963.1496)</t>
+  </si>
+  <si>
+    <t>(7429.8022, 9532.2653, 16962.0676)</t>
+  </si>
+  <si>
+    <t>(6248.1292, 10712.966, 16961.0952)</t>
+  </si>
+  <si>
+    <t>TFPR1_LIST_1</t>
+  </si>
+  <si>
+    <t>+12, ???, [12, 7], (0.097, 'n/a'), [14033]|</t>
+  </si>
+  <si>
+    <t>+16, ???, [3, 16], (0.081, 'n/a'), [8096]|</t>
+  </si>
+  <si>
+    <t>???, 0, [13, 6], ('n/a', 0.087), [4772]|</t>
+  </si>
+  <si>
+    <t>+6, ???, [17, 2], (0.086, 'n/a'), [2687]|</t>
+  </si>
+  <si>
+    <t>+19, ???, [3, 16], (0.08, 'n/a'), [3353]|</t>
+  </si>
+  <si>
+    <t>+18, ???, [5, 14], (0.09, 'n/a'), [982]|</t>
+  </si>
+  <si>
+    <t>???, +18, [15, 4], ('n/a', 0.095), [15687]|</t>
+  </si>
+  <si>
+    <t>+16, ???, [13, 6], (0.082, 'n/a'), [12299]|</t>
+  </si>
+  <si>
+    <t>???, +16, [3, 16], ('n/a', 0.08), [15788]|</t>
+  </si>
+  <si>
+    <t>+14, ???, [9, 10], (0.098, 'n/a'), [4168]|</t>
+  </si>
+  <si>
+    <t>???, +9, [7, 12], ('n/a', 0.016), [8507]|</t>
+  </si>
+  <si>
+    <t>+18, ???, [2, 17], (0.037, 'n/a'), [11258]|</t>
+  </si>
+  <si>
+    <t>???, +12, [11, 7], ('n/a', 0.066), [3277]|</t>
+  </si>
+  <si>
+    <t>+4, ???, [14, 5], (0.008, 'n/a'), [14164]|</t>
+  </si>
+  <si>
+    <t>???, +3, [17, 2], ('n/a', 0.091), [11090]|</t>
+  </si>
+  <si>
+    <t>FPR1_LIST_3</t>
+  </si>
+  <si>
+    <t>???, +8, [1, 18], ('n/a', 0.085), [14303]|</t>
+  </si>
+  <si>
+    <t>+16, ???, [3, 16], (0.089, 'n/a'), [15687]|</t>
+  </si>
+  <si>
+    <t>???, +13, [8, 11], ('n/a', 0.092), [5000]|</t>
+  </si>
+  <si>
+    <t>+19, ???, [1, 18], (0.006, 'n/a'), [7684]|</t>
+  </si>
+  <si>
+    <t>???, +19, [7, 12], ('n/a', 0.053), [5512]|</t>
+  </si>
+  <si>
+    <t>???, +13, [14, 4], ('n/a', 0.077), [4760]|</t>
+  </si>
+  <si>
+    <t>???, +16, [11, 8], ('n/a', 0.087), [15010]|</t>
+  </si>
+  <si>
+    <t>+15, ???, [1, 18], (0.006, 'n/a'), [16365]|</t>
+  </si>
+  <si>
+    <t>???, +19, [13, 6], ('n/a', 0.033), [12706]|</t>
+  </si>
+  <si>
+    <t>+12, ???, [5, 14], (0.016, 'n/a'), [16526]|</t>
+  </si>
+  <si>
+    <t>+11, ???, [6, 12], (0.067, 'n/a'), [6182]|</t>
+  </si>
+  <si>
+    <t>+8, ???, [14, 5], (0.052, 'n/a'), [4538]|</t>
+  </si>
+  <si>
+    <t>???, +18, [5, 14], ('n/a', 0.05), [11695]|</t>
+  </si>
+  <si>
+    <t>???, +10, [12, 7], ('n/a', 0.069), [11822]|</t>
+  </si>
+  <si>
+    <t>+14, ???, [1, 17], (0.097, 'n/a'), [4023]|</t>
+  </si>
+  <si>
+    <t>???, +7, [8, 11], ('n/a', 0.063), [5734]|</t>
+  </si>
+  <si>
+    <t>+7, ???, [7, 12], (0.031, 'n/a'), [18105]|</t>
+  </si>
+  <si>
+    <t>???, +4, [7, 12], ('n/a', 0.035), [11673]|</t>
+  </si>
+  <si>
+    <t>FPR1_LIST_2</t>
+  </si>
+  <si>
+    <t>+4, ???, [9, 10], (0.079, 'n/a'), [15191]|</t>
+  </si>
+  <si>
+    <t>???, +2, [12, 7], ('n/a', 0.051), [12078]|</t>
+  </si>
+  <si>
+    <t>???, +20, [16, 3], ('n/a', 0.03), [15687]|</t>
+  </si>
+  <si>
+    <t>+19, ???, [8, 10], (0.1, 'n/a'), [17301]|</t>
+  </si>
+  <si>
+    <t>???, +16, [3, 16], ('n/a', 0.08), [17407]|</t>
+  </si>
+  <si>
+    <t>+3, ???, [2, 17], (0.075, 'n/a'), [5714]|</t>
+  </si>
+  <si>
+    <t>+15, ???, [5, 14], (0.069, 'n/a'), [12639]|</t>
+  </si>
+  <si>
+    <t>???, +17, [15, 4], ('n/a', 0.075), [19735]|</t>
+  </si>
+  <si>
+    <t>???, +4, [16, 3], ('n/a', 0.094), [16946]|</t>
+  </si>
+  <si>
+    <t>+19, ???, [13, 6], (0.08, 'n/a'), [13503]|</t>
+  </si>
+  <si>
+    <t>???, +9, [14, 5], ('n/a', 0.096), [18832]|</t>
+  </si>
+  <si>
+    <t>???, +2, [1, 18], ('n/a', 0.06), [10219]|</t>
+  </si>
+  <si>
+    <t>+11, ???, [13, 6], (0.046, 'n/a'), [16753]|</t>
+  </si>
+  <si>
+    <t>???, +9, [8, 11], ('n/a', 0.029), [16090]|</t>
+  </si>
+  <si>
+    <t>???, +1, [18, 1], ('n/a', 0.091), [12751]|</t>
+  </si>
+  <si>
+    <t>???, +10, [17, 2], ('n/a', 0.003), [17512]|</t>
+  </si>
+  <si>
+    <t>???, +7, [2, 17], ('n/a', 0.008), [6300]|</t>
+  </si>
+  <si>
+    <t>???, +18, [2, 16], ('n/a', 0.076), [18666]|</t>
+  </si>
+  <si>
+    <t>???, +18, [8, 10], ('n/a', 0.033), [19575]|</t>
+  </si>
+  <si>
+    <t>???, +2, [7, 12], ('n/a', 0.07), [18179]|</t>
+  </si>
+  <si>
+    <t>FPR1_LIST_1</t>
+  </si>
+  <si>
+    <t>(13914.2049, 3065.9231, 16980.1279)</t>
+  </si>
+  <si>
+    <t>(5278.4425, 11700.613, 16979.0555)</t>
+  </si>
+  <si>
+    <t>(8896.1529, 8081.9106, 16978.0635)</t>
+  </si>
+  <si>
+    <t>(15129.6958, 1847.4552, 16977.151)</t>
+  </si>
+  <si>
+    <t>(11430.4696, 5545.6586, 16976.1282)</t>
+  </si>
+  <si>
+    <t>(2670.5013, 14304.6328, 16975.134)</t>
+  </si>
+  <si>
+    <t>(8843.2205, 8130.9039, 16974.1244)</t>
+  </si>
+  <si>
+    <t>(2675.6408, 14297.4973, 16973.1381)</t>
+  </si>
+  <si>
+    <t>(7081.3133, 9890.7453, 16972.0587)</t>
+  </si>
+  <si>
+    <t>(7144.5086, 9826.5784, 16971.087)</t>
+  </si>
+  <si>
+    <t>(14151.692, 2818.4594, 16970.1514)</t>
+  </si>
+  <si>
+    <t>(8930.6357, 8038.5122, 16969.148)</t>
+  </si>
+  <si>
+    <t>(4455.3133, 12512.7736, 16968.0868)</t>
+  </si>
+  <si>
+    <t>(5291.0857, 11676.0293, 16967.115)</t>
+  </si>
+  <si>
+    <t>(4463.9975, 12502.1491, 16966.1466)</t>
+  </si>
+  <si>
+    <t>(11173.3866, 5791.7441, 16965.1306)</t>
+  </si>
+  <si>
+    <t>(1834.8742, 15129.2088, 16964.083)</t>
+  </si>
+  <si>
+    <t>(6500.2982, 10462.8195, 16963.1176)</t>
+  </si>
+  <si>
+    <t>(6235.2254, 10726.8359, 16962.0613)</t>
+  </si>
+  <si>
+    <t>(10607.4394, 6353.6323, 16961.0717)</t>
+  </si>
+  <si>
+    <t>(8915.8921, 8044.1848, 16960.0769)</t>
+  </si>
+  <si>
+    <t>TFPR0_LIST_3</t>
+  </si>
+  <si>
+    <t>(4628.6519, 12351.4405, 16980.0924)</t>
+  </si>
+  <si>
+    <t>(4457.8151, 12521.2732, 16979.0883)</t>
+  </si>
+  <si>
+    <t>(15150.7423, 1827.313, 16978.0553)</t>
+  </si>
+  <si>
+    <t>(12345.8667, 4631.2366, 16977.1033)</t>
+  </si>
+  <si>
+    <t>(5537.3396, 11438.7184, 16976.058)</t>
+  </si>
+  <si>
+    <t>(1820.4377, 15154.6481, 16975.0858)</t>
+  </si>
+  <si>
+    <t>(15144.0191, 1830.0584, 16974.0775)</t>
+  </si>
+  <si>
+    <t>(3974.0125, 12999.0403, 16973.0528)</t>
+  </si>
+  <si>
+    <t>(7101.5462, 9870.5793, 16972.1255)</t>
+  </si>
+  <si>
+    <t>(13237.977, 3733.125, 16971.1021)</t>
+  </si>
+  <si>
+    <t>(893.0636, 16077.0244, 16970.088)</t>
+  </si>
+  <si>
+    <t>(16047.1057, 922.0009, 16969.1065)</t>
+  </si>
+  <si>
+    <t>(12449.0747, 4518.9972, 16968.0718)</t>
+  </si>
+  <si>
+    <t>(4570.5806, 12396.5529, 16967.1334)</t>
+  </si>
+  <si>
+    <t>(12251.7854, 4714.3647, 16966.1501)</t>
+  </si>
+  <si>
+    <t>(8927.995, 8037.0958, 16965.0908)</t>
+  </si>
+  <si>
+    <t>(8412.1216, 8551.9953, 16964.1169)</t>
+  </si>
+  <si>
+    <t>(2661.9719, 14301.16, 16963.1319)</t>
+  </si>
+  <si>
+    <t>(6536.0868, 10425.9935, 16962.0803)</t>
+  </si>
+  <si>
+    <t>(2671.2877, 14289.8518, 16961.1395)</t>
+  </si>
+  <si>
+    <t>(1668.7666, 15291.3253, 16960.0919)</t>
+  </si>
+  <si>
+    <t>TFPR0_LIST_2</t>
+  </si>
+  <si>
+    <t>(13121.6111, 3858.4614, 16980.0725)</t>
+  </si>
+  <si>
+    <t>(15143.1088, 1835.9991, 16979.1079)</t>
+  </si>
+  <si>
+    <t>(916.3875, 16061.7408, 16978.1283)</t>
+  </si>
+  <si>
+    <t>(12332.2606, 4644.8914, 16977.1521)</t>
+  </si>
+  <si>
+    <t>(5403.9477, 11572.1491, 16976.0968)</t>
+  </si>
+  <si>
+    <t>(14179.4657, 2795.675, 16975.1407)</t>
+  </si>
+  <si>
+    <t>(7433.5839, 9540.4958, 16974.0797)</t>
+  </si>
+  <si>
+    <t>(2676.5061, 14296.5836, 16973.0897)</t>
+  </si>
+  <si>
+    <t>(13086.2838, 3885.833, 16972.1167)</t>
+  </si>
+  <si>
+    <t>(4457.946, 12513.1764, 16971.1224)</t>
+  </si>
+  <si>
+    <t>(13367.9021, 3602.1854, 16970.0875)</t>
+  </si>
+  <si>
+    <t>(4771.0704, 12198.0689, 16969.1394)</t>
+  </si>
+  <si>
+    <t>(13260.8807, 3707.2008, 16968.0815)</t>
+  </si>
+  <si>
+    <t>(11466.4612, 5500.634, 16967.0952)</t>
+  </si>
+  <si>
+    <t>(16014.9052, 951.1654, 16966.0706)</t>
+  </si>
+  <si>
+    <t>(937.3176, 16027.7671, 16965.0847)</t>
+  </si>
+  <si>
+    <t>(15119.4127, 1844.6649, 16964.0776)</t>
+  </si>
+  <si>
+    <t>(9812.9884, 7150.1563, 16963.1448)</t>
+  </si>
+  <si>
+    <t>(15168.6635, 1793.4431, 16962.1066)</t>
+  </si>
+  <si>
+    <t>(8923.0115, 8038.0416, 16961.0531)</t>
+  </si>
+  <si>
+    <t>(5329.1377, 11630.9824, 16960.1201)</t>
+  </si>
+  <si>
+    <t>TFPR0_LIST_1</t>
+  </si>
+  <si>
+    <t>FPR0_LIST_3</t>
+  </si>
+  <si>
+    <t>FPR0_LIST_2</t>
+  </si>
+  <si>
+    <t>FPR0_LIST_1</t>
+  </si>
+  <si>
+    <t>+3, +17, [17, 2], (0.039, 0.007), [15513]</t>
+  </si>
+  <si>
+    <t>(3, 17)</t>
+  </si>
+  <si>
+    <t>+9, +2, [17, 2], (0.005, 0.036), [14283]</t>
+  </si>
+  <si>
+    <t>(9, 2)</t>
+  </si>
+  <si>
+    <t>+15, +4, [16, 3], (0.033, 0.003), [6489]</t>
+  </si>
+  <si>
+    <t>(15, 4)</t>
+  </si>
+  <si>
+    <t>+1, +18, [15, 3], (0.024, 0.04), [12604]</t>
+  </si>
+  <si>
+    <t>(1, 18)</t>
+  </si>
+  <si>
+    <t>+7, +7, [15, 4], (0.041, 0.097), [10493]</t>
+  </si>
+  <si>
+    <t>+5, +4, [14, 5], (0.026, 0.008), [5449]</t>
+  </si>
+  <si>
+    <t>+2, +3, [15, 4], (0.032, 0.02), [12566]</t>
+  </si>
+  <si>
+    <t>+13, +7, [15, 4], (0.035, 0.007), [12874]</t>
+  </si>
+  <si>
+    <t>+5, +1, [14, 5], (0.003, 0.012), [11247]</t>
+  </si>
+  <si>
+    <t>+6, +2, [14, 5], (0.034, 0.02), [13808]</t>
+  </si>
+  <si>
+    <t>(6, 2)</t>
+  </si>
+  <si>
+    <t>+10, +2, [13, 5], (0.07, 0.081), [13556]</t>
+  </si>
+  <si>
+    <t>+5, +4, [13, 6], (0.045, 0.014), [1919]</t>
+  </si>
+  <si>
+    <t>(4, 3)</t>
+  </si>
+  <si>
+    <t>+4, 0, [12, 7], (0.078, 0.054), [19987]</t>
+  </si>
+  <si>
+    <t>(4, 0)</t>
+  </si>
+  <si>
+    <t>+10, +2, [11, 8], (0.023, 0.02), [15637]</t>
+  </si>
+  <si>
+    <t>+3, +5, [11, 8], (0.087, 0.017), [12880]</t>
+  </si>
+  <si>
+    <t>+9, +1, [12, 7], (0.084, 0.069), [16832]</t>
+  </si>
+  <si>
+    <t>(9, 1)</t>
+  </si>
+  <si>
+    <t>+11, +4, [10, 9], (0.028, 0.052), [14950]</t>
+  </si>
+  <si>
+    <t>(11, 4)</t>
+  </si>
+  <si>
+    <t>+3, +1, [10, 9], (0.031, 0.075), [10481]</t>
+  </si>
+  <si>
+    <t>(3, 1)</t>
+  </si>
+  <si>
+    <t>+8, +8, [9, 10], (0.079, 0.024), [7673]</t>
+  </si>
+  <si>
+    <t>(8, 8)</t>
+  </si>
+  <si>
+    <t>+7, +8, [9, 10], (0.0, 0.024), [14950]</t>
+  </si>
+  <si>
+    <t>(7, 8)</t>
+  </si>
+  <si>
+    <t>+3, +9, [8, 11], (0.035, 0.025), [18680]</t>
+  </si>
+  <si>
+    <t>+6, +5, [8, 11], (0.014, 0.078), [10132]</t>
+  </si>
+  <si>
+    <t>+1, +5, [8, 11], (0.057, 0.078), [10156]</t>
+  </si>
+  <si>
+    <t>(1, 5)</t>
+  </si>
+  <si>
+    <t>+3, +12, [6, 12], (0.022, 0.065), [2794]</t>
+  </si>
+  <si>
+    <t>(2, 11)</t>
+  </si>
+  <si>
+    <t>+2, +5, [4, 15], (0.017, 0.024), [10462]</t>
+  </si>
+  <si>
+    <t>(2, 5)</t>
+  </si>
+  <si>
+    <t>+4, +12, [4, 15], (0.024, 0.008), [19440]</t>
+  </si>
+  <si>
+    <t>(4, 12)</t>
+  </si>
+  <si>
+    <t>+3, +10, [3, 16], (0.042, 0.035), [18716]</t>
+  </si>
+  <si>
+    <t>0, +6, [3, 16], (0.006, 0.019), [15509]</t>
+  </si>
+  <si>
+    <t>+20, +1, [3, 15], (0.021, 0.059), [10020]</t>
+  </si>
+  <si>
+    <t>+14, +5, [1, 17], (0.066, 0.015), [8263]</t>
+  </si>
+  <si>
+    <t>+19, ???, [1, 18], (0.006, 'n/a'), [7684]</t>
+  </si>
+  <si>
+    <t>+5, +2, [1, 18], (0.076, 0.06), [15354]</t>
+  </si>
+  <si>
+    <t>N=20000</t>
+  </si>
+  <si>
+    <t>(888.189618, 894.69095, [6, 13], 19735)</t>
+  </si>
+  <si>
+    <t>(892.30115, 893.115737, [10, 9], 17352)</t>
+  </si>
+  <si>
+    <t>(892.274323, 896.72156, [17, 2], 19565)</t>
+  </si>
+  <si>
+    <t>(892.089858, 893.769541, [11, 8], 19587)</t>
+  </si>
+  <si>
+    <t>(889.37722, 922.332452, [17, 2], 19164)</t>
+  </si>
+  <si>
+    <t>(937.31756, 942.809832, [1, 17], 19405)</t>
+  </si>
+  <si>
+    <t>(889.716958, 951.165405, [18, 1], 19413)</t>
+  </si>
+  <si>
+    <t>(882.035478, 916.772339, [13, 6], 18734)</t>
+  </si>
+  <si>
+    <t>(884.058715, 926.800197, [15, 4], 19426)</t>
+  </si>
+  <si>
+    <t>(795.178403, 938.312995, [6, 13], 19981)</t>
+  </si>
+  <si>
+    <t>(891.193476, 900.546338, [15, 4], 19984)</t>
+  </si>
+  <si>
+    <t>(891.589207, 893.798312, [5, 14], 18753)</t>
+  </si>
+  <si>
+    <t>(934.734554, 971.458242, [14, 4], 19749)</t>
+  </si>
+  <si>
+    <t>(892.168687, 953.105575, [3, 15], 19890)</t>
+  </si>
+  <si>
+    <t>(929.197989, 954.049583, [8, 10], 19644)</t>
+  </si>
+  <si>
+    <t>(886.216606, 931.891681, [16, 3], 19960)</t>
+  </si>
+  <si>
+    <t>(900.657956, 964.345756, [6, 12], 18962)</t>
+  </si>
+  <si>
+    <t>(880.875759, 928.978288, [14, 5], 19997)</t>
+  </si>
+  <si>
+    <t>(916.387507, 944.808281, [1, 17], 19929)</t>
+  </si>
+  <si>
+    <t>(890.771105, 917.99954, [17, 2], 19713)</t>
+  </si>
+  <si>
+    <t>(937.257937, 964.615348, [14, 4], 18382)</t>
+  </si>
+  <si>
+    <t>(834.383318, 899.489723, [2, 17], 18888)</t>
+  </si>
+  <si>
+    <t>(890.429223, 893.115737, [3, 16], 17064)</t>
+  </si>
+  <si>
+    <t>(933.726686, 947.817589, [7, 11], 18000)</t>
+  </si>
+  <si>
+    <t>(887.32396, 893.822502, [3, 16], 19467)</t>
+  </si>
+  <si>
+    <t>(934.680178, 950.221699, [9, 9], 19068)</t>
+  </si>
+  <si>
+    <t>(892.799498, 893.010649, [10, 9], 17793)</t>
+  </si>
+  <si>
+    <t>(942.44503, 942.872949, [13, 5], 18534)</t>
+  </si>
+  <si>
+    <t>(914.116113, 953.58099, [5, 13], 18669)</t>
+  </si>
+  <si>
+    <t>(889.219618, 903.799435, [14, 5], 19322)</t>
+  </si>
+  <si>
+    <t>(891.50587, 922.000882, [18, 1], 19954)</t>
+  </si>
+  <si>
+    <t>(893.063573, 893.168025, [1, 18], 19885)</t>
+  </si>
+  <si>
+    <t>(882.531803, 933.281258, [15, 4], 17654)</t>
+  </si>
+  <si>
+    <t>(887.693281, 897.325389, [8, 11], 19543)</t>
+  </si>
+  <si>
+    <t>(794.802496, 928.50288, [5, 14], 18202)</t>
+  </si>
+  <si>
+    <t>(890.824654, 915.029195, [17, 2], 19461)</t>
+  </si>
+  <si>
+    <t>(910.218868, 947.165504, [2, 16], 19855)</t>
+  </si>
+  <si>
+    <t>(922.889938, 953.226534, [6, 12], 18424)</t>
+  </si>
+  <si>
+    <t>(881.847623, 926.247317, [14, 5], 18694)</t>
+  </si>
+  <si>
+    <t>(891.220136, 913.6565, [17, 2], 19924)</t>
+  </si>
+  <si>
+    <t>(891.563016, 894.376658, [5, 14], 19681)</t>
+  </si>
+  <si>
+    <t>(925.730377, 950.110808, [5, 13], 18104)</t>
+  </si>
+  <si>
+    <t>(891.589207, 893.798312, [10, 9], 18753)</t>
+  </si>
+  <si>
+    <t>(883.953282, 907.661753, [12, 7], 17003)</t>
+  </si>
+  <si>
+    <t>(890.746485, 893.902992, [7, 12], 17787)</t>
+  </si>
+  <si>
+    <t>(928.614024, 951.165405, [7, 11], 18333)</t>
+  </si>
+  <si>
+    <t>(917.4371, 945.575549, [2, 16], 18129)</t>
+  </si>
+  <si>
+    <t>(931.115547, 965.290677, [12, 6], 17672)</t>
+  </si>
+  <si>
+    <t>(892.799498, 893.010649, [5, 14], 17793)</t>
+  </si>
+  <si>
+    <t>(881.847623, 898.156097, [6, 13], 18365)</t>
+  </si>
+  <si>
+    <t>(891.062654, 893.769541, [5, 14], 19086)</t>
+  </si>
+  <si>
+    <t>(893.063573, 893.168025, [10, 9], 19885)</t>
+  </si>
+  <si>
+    <t>(884.480751, 939.486457, [16, 3], 19789)</t>
+  </si>
+  <si>
+    <t>(893.063573, 893.325308, [8, 11], 17318)</t>
+  </si>
+  <si>
+    <t>(885.164168, 899.158666, [8, 11], 19337)</t>
+  </si>
+  <si>
+    <t>(891.880255, 953.166489, [3, 15], 17135)</t>
+  </si>
+  <si>
+    <t>(884.322054, 903.433763, [10, 9], 18810)</t>
+  </si>
+  <si>
+    <t>(890.167085, 894.039549, [3, 16], 18700)</t>
+  </si>
+  <si>
+    <t>(879.266892, 924.276427, [13, 6], 18312)</t>
+  </si>
+  <si>
+    <t>(889.982107, 923.727597, [17, 2], 18507)</t>
+  </si>
+  <si>
+    <t>(889.615294, 897.990067, [10, 9], 19550)</t>
+  </si>
+  <si>
+    <t>(879.740411, 900.047157, [6, 13], 18767)</t>
+  </si>
+  <si>
+    <t>(927.613659, 1021.974354, [15, 3], 16387)</t>
   </si>
 </sst>
 </file>
@@ -4113,14 +4521,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="20" width="49.1640625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="32.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
-        <v>1213</v>
+        <v>1057</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4987,20 +5392,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AH25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="34" width="39.33203125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="32.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:34">
       <c r="A1" s="4" t="s">
-        <v>1213</v>
+        <v>1057</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>906</v>
+        <v>750</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>385</v>
@@ -5015,7 +5417,7 @@
         <v>2</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>1210</v>
+        <v>1054</v>
       </c>
       <c r="I1" s="2">
         <v>-666.36199999999997</v>
@@ -5024,7 +5426,7 @@
         <v>-665.35900000000004</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>1211</v>
+        <v>1055</v>
       </c>
       <c r="L1" s="2">
         <v>-406.18799999999999</v>
@@ -5033,7 +5435,7 @@
         <v>-405.18700000000001</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>907</v>
+        <v>751</v>
       </c>
       <c r="O1" s="2">
         <v>-390.23099999999999</v>
@@ -5042,7 +5444,7 @@
         <v>-389.22899999999998</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>1212</v>
+        <v>1056</v>
       </c>
       <c r="R1" s="2">
         <v>-277.14600000000002</v>
@@ -5054,7 +5456,7 @@
         <v>-275.14100000000002</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>908</v>
+        <v>752</v>
       </c>
       <c r="V1" s="2">
         <v>-113.08</v>
@@ -5063,7 +5465,7 @@
         <v>-112.09099999999999</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>909</v>
+        <v>753</v>
       </c>
       <c r="Y1" s="2">
         <v>-26.988</v>
@@ -5098,10 +5500,10 @@
     </row>
     <row r="2" spans="1:34">
       <c r="A2" s="2" t="s">
-        <v>910</v>
+        <v>754</v>
       </c>
       <c r="B2" t="s">
-        <v>698</v>
+        <v>628</v>
       </c>
       <c r="C2" t="s">
         <v>140</v>
@@ -5110,12 +5512,12 @@
         <v>0</v>
       </c>
       <c r="AH2" t="s">
-        <v>911</v>
+        <v>755</v>
       </c>
     </row>
     <row r="3" spans="1:34">
       <c r="A3" s="2" t="s">
-        <v>912</v>
+        <v>756</v>
       </c>
       <c r="B3" t="s">
         <v>106</v>
@@ -5127,39 +5529,39 @@
         <v>143</v>
       </c>
       <c r="O3" t="s">
-        <v>913</v>
+        <v>757</v>
       </c>
       <c r="P3" t="s">
-        <v>914</v>
+        <v>758</v>
       </c>
       <c r="Q3" t="s">
         <v>19</v>
       </c>
       <c r="T3" t="s">
-        <v>915</v>
+        <v>759</v>
       </c>
       <c r="X3" t="s">
         <v>19</v>
       </c>
       <c r="Y3" t="s">
-        <v>916</v>
+        <v>760</v>
       </c>
       <c r="Z3" t="s">
-        <v>917</v>
+        <v>761</v>
       </c>
       <c r="AA3" t="s">
-        <v>918</v>
+        <v>762</v>
       </c>
       <c r="AG3">
         <v>7</v>
       </c>
       <c r="AH3" t="s">
-        <v>919</v>
+        <v>763</v>
       </c>
     </row>
     <row r="4" spans="1:34">
       <c r="A4" s="2" t="s">
-        <v>920</v>
+        <v>764</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -5171,39 +5573,39 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>921</v>
+        <v>765</v>
       </c>
       <c r="F4" t="s">
-        <v>922</v>
+        <v>766</v>
       </c>
       <c r="G4" t="s">
-        <v>923</v>
+        <v>767</v>
       </c>
       <c r="X4" t="s">
         <v>143</v>
       </c>
       <c r="Y4" t="s">
-        <v>924</v>
+        <v>768</v>
       </c>
       <c r="Z4" t="s">
-        <v>925</v>
+        <v>769</v>
       </c>
       <c r="AB4" t="s">
-        <v>926</v>
+        <v>770</v>
       </c>
       <c r="AC4" t="s">
-        <v>927</v>
+        <v>771</v>
       </c>
       <c r="AG4">
         <v>7</v>
       </c>
       <c r="AH4" t="s">
-        <v>928</v>
+        <v>772</v>
       </c>
     </row>
     <row r="5" spans="1:34">
       <c r="A5" s="2" t="s">
-        <v>929</v>
+        <v>773</v>
       </c>
       <c r="B5" t="s">
         <v>155</v>
@@ -5215,63 +5617,63 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>930</v>
+        <v>774</v>
       </c>
       <c r="F5" t="s">
-        <v>931</v>
+        <v>775</v>
       </c>
       <c r="G5" t="s">
-        <v>932</v>
+        <v>776</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
       </c>
       <c r="J5" t="s">
-        <v>933</v>
+        <v>777</v>
       </c>
       <c r="Q5" t="s">
         <v>143</v>
       </c>
       <c r="T5" t="s">
-        <v>934</v>
+        <v>778</v>
       </c>
       <c r="U5" t="s">
         <v>19</v>
       </c>
       <c r="V5" t="s">
-        <v>935</v>
+        <v>779</v>
       </c>
       <c r="W5" t="s">
-        <v>936</v>
+        <v>780</v>
       </c>
       <c r="X5" t="s">
         <v>19</v>
       </c>
       <c r="Y5" t="s">
-        <v>937</v>
+        <v>781</v>
       </c>
       <c r="Z5" t="s">
-        <v>938</v>
+        <v>782</v>
       </c>
       <c r="AC5" t="s">
-        <v>939</v>
+        <v>783</v>
       </c>
       <c r="AE5" t="s">
-        <v>940</v>
+        <v>784</v>
       </c>
       <c r="AF5" t="s">
-        <v>941</v>
+        <v>785</v>
       </c>
       <c r="AG5">
         <v>14</v>
       </c>
       <c r="AH5" t="s">
-        <v>942</v>
+        <v>786</v>
       </c>
     </row>
     <row r="6" spans="1:34">
       <c r="A6" s="2" t="s">
-        <v>943</v>
+        <v>787</v>
       </c>
       <c r="B6" t="s">
         <v>38</v>
@@ -5283,72 +5685,72 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>944</v>
+        <v>788</v>
       </c>
       <c r="F6" t="s">
-        <v>945</v>
+        <v>789</v>
       </c>
       <c r="G6" t="s">
-        <v>946</v>
+        <v>790</v>
       </c>
       <c r="K6" t="s">
         <v>42</v>
       </c>
       <c r="L6" t="s">
-        <v>947</v>
+        <v>791</v>
       </c>
       <c r="M6" t="s">
-        <v>948</v>
+        <v>792</v>
       </c>
       <c r="N6" t="s">
         <v>42</v>
       </c>
       <c r="O6" t="s">
-        <v>949</v>
+        <v>793</v>
       </c>
       <c r="P6" t="s">
-        <v>950</v>
+        <v>794</v>
       </c>
       <c r="Q6" t="s">
         <v>19</v>
       </c>
       <c r="S6" t="s">
-        <v>951</v>
+        <v>795</v>
       </c>
       <c r="T6" t="s">
-        <v>952</v>
+        <v>796</v>
       </c>
       <c r="U6" t="s">
         <v>19</v>
       </c>
       <c r="V6" t="s">
-        <v>953</v>
+        <v>797</v>
       </c>
       <c r="W6" t="s">
-        <v>954</v>
+        <v>798</v>
       </c>
       <c r="X6" t="s">
         <v>19</v>
       </c>
       <c r="Y6" t="s">
-        <v>955</v>
+        <v>799</v>
       </c>
       <c r="Z6" t="s">
-        <v>956</v>
+        <v>800</v>
       </c>
       <c r="AF6" t="s">
-        <v>957</v>
+        <v>801</v>
       </c>
       <c r="AG6">
         <v>16</v>
       </c>
       <c r="AH6" t="s">
-        <v>958</v>
+        <v>802</v>
       </c>
     </row>
     <row r="7" spans="1:34">
       <c r="A7" s="2" t="s">
-        <v>959</v>
+        <v>803</v>
       </c>
       <c r="B7" t="s">
         <v>152</v>
@@ -5360,57 +5762,57 @@
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>960</v>
+        <v>804</v>
       </c>
       <c r="F7" t="s">
-        <v>961</v>
+        <v>805</v>
       </c>
       <c r="G7" t="s">
-        <v>962</v>
+        <v>806</v>
       </c>
       <c r="N7" t="s">
         <v>19</v>
       </c>
       <c r="O7" t="s">
-        <v>963</v>
+        <v>807</v>
       </c>
       <c r="P7" t="s">
-        <v>964</v>
+        <v>808</v>
       </c>
       <c r="Q7" t="s">
         <v>42</v>
       </c>
       <c r="R7" t="s">
-        <v>965</v>
+        <v>809</v>
       </c>
       <c r="S7" t="s">
-        <v>966</v>
+        <v>810</v>
       </c>
       <c r="U7" t="s">
         <v>19</v>
       </c>
       <c r="V7" t="s">
-        <v>967</v>
+        <v>811</v>
       </c>
       <c r="W7" t="s">
-        <v>968</v>
+        <v>812</v>
       </c>
       <c r="AE7" t="s">
-        <v>969</v>
+        <v>813</v>
       </c>
       <c r="AF7" t="s">
-        <v>970</v>
+        <v>814</v>
       </c>
       <c r="AG7">
         <v>11</v>
       </c>
       <c r="AH7" t="s">
-        <v>971</v>
+        <v>815</v>
       </c>
     </row>
     <row r="8" spans="1:34">
       <c r="A8" s="2" t="s">
-        <v>972</v>
+        <v>816</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
@@ -5422,42 +5824,42 @@
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>973</v>
+        <v>817</v>
       </c>
       <c r="F8" t="s">
-        <v>974</v>
+        <v>818</v>
       </c>
       <c r="G8" t="s">
-        <v>975</v>
+        <v>819</v>
       </c>
       <c r="K8" t="s">
         <v>19</v>
       </c>
       <c r="L8" t="s">
-        <v>976</v>
+        <v>820</v>
       </c>
       <c r="M8" t="s">
-        <v>977</v>
+        <v>821</v>
       </c>
       <c r="Q8" t="s">
         <v>143</v>
       </c>
       <c r="R8" t="s">
-        <v>978</v>
+        <v>822</v>
       </c>
       <c r="S8" t="s">
-        <v>979</v>
+        <v>823</v>
       </c>
       <c r="AG8">
         <v>7</v>
       </c>
       <c r="AH8" t="s">
-        <v>980</v>
+        <v>824</v>
       </c>
     </row>
     <row r="9" spans="1:34">
       <c r="A9" s="2" t="s">
-        <v>981</v>
+        <v>825</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -5469,51 +5871,51 @@
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>982</v>
+        <v>826</v>
       </c>
       <c r="F9" t="s">
-        <v>983</v>
+        <v>827</v>
       </c>
       <c r="K9" t="s">
         <v>42</v>
       </c>
       <c r="L9" t="s">
-        <v>984</v>
+        <v>828</v>
       </c>
       <c r="Q9" t="s">
         <v>42</v>
       </c>
       <c r="R9" t="s">
-        <v>985</v>
+        <v>829</v>
       </c>
       <c r="S9" t="s">
-        <v>986</v>
+        <v>830</v>
       </c>
       <c r="U9" t="s">
         <v>19</v>
       </c>
       <c r="V9" t="s">
-        <v>987</v>
+        <v>831</v>
       </c>
       <c r="AD9" t="s">
-        <v>988</v>
+        <v>832</v>
       </c>
       <c r="AE9" t="s">
-        <v>989</v>
+        <v>833</v>
       </c>
       <c r="AF9" t="s">
-        <v>990</v>
+        <v>834</v>
       </c>
       <c r="AG9">
         <v>9</v>
       </c>
       <c r="AH9" t="s">
-        <v>991</v>
+        <v>835</v>
       </c>
     </row>
     <row r="10" spans="1:34">
       <c r="A10" s="2" t="s">
-        <v>992</v>
+        <v>836</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
@@ -5525,69 +5927,69 @@
         <v>42</v>
       </c>
       <c r="F10" t="s">
-        <v>993</v>
+        <v>837</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10" t="s">
-        <v>994</v>
+        <v>838</v>
       </c>
       <c r="K10" t="s">
         <v>42</v>
       </c>
       <c r="L10" t="s">
-        <v>995</v>
+        <v>839</v>
       </c>
       <c r="N10" t="s">
         <v>42</v>
       </c>
       <c r="O10" t="s">
-        <v>996</v>
+        <v>840</v>
       </c>
       <c r="P10" t="s">
-        <v>997</v>
+        <v>841</v>
       </c>
       <c r="Q10" t="s">
         <v>42</v>
       </c>
       <c r="R10" t="s">
-        <v>998</v>
+        <v>842</v>
       </c>
       <c r="S10" t="s">
-        <v>999</v>
+        <v>843</v>
       </c>
       <c r="T10" t="s">
-        <v>1000</v>
+        <v>844</v>
       </c>
       <c r="U10" t="s">
         <v>19</v>
       </c>
       <c r="V10" t="s">
-        <v>1001</v>
+        <v>845</v>
       </c>
       <c r="W10" t="s">
-        <v>1002</v>
+        <v>846</v>
       </c>
       <c r="AD10" t="s">
-        <v>1003</v>
+        <v>847</v>
       </c>
       <c r="AE10" t="s">
-        <v>1004</v>
+        <v>848</v>
       </c>
       <c r="AF10" t="s">
-        <v>1005</v>
+        <v>849</v>
       </c>
       <c r="AG10">
         <v>13</v>
       </c>
       <c r="AH10" t="s">
-        <v>1006</v>
+        <v>850</v>
       </c>
     </row>
     <row r="11" spans="1:34">
       <c r="A11" s="2" t="s">
-        <v>1007</v>
+        <v>851</v>
       </c>
       <c r="B11" t="s">
         <v>38</v>
@@ -5599,57 +6001,57 @@
         <v>42</v>
       </c>
       <c r="I11" t="s">
-        <v>1008</v>
+        <v>852</v>
       </c>
       <c r="J11" t="s">
-        <v>1009</v>
+        <v>853</v>
       </c>
       <c r="K11" t="s">
         <v>42</v>
       </c>
       <c r="L11" t="s">
-        <v>1010</v>
+        <v>854</v>
       </c>
       <c r="N11" t="s">
         <v>42</v>
       </c>
       <c r="O11" t="s">
-        <v>1011</v>
+        <v>855</v>
       </c>
       <c r="P11" t="s">
-        <v>1012</v>
+        <v>856</v>
       </c>
       <c r="Q11" t="s">
         <v>42</v>
       </c>
       <c r="R11" t="s">
-        <v>1013</v>
+        <v>857</v>
       </c>
       <c r="S11" t="s">
-        <v>1014</v>
+        <v>858</v>
       </c>
       <c r="U11" t="s">
         <v>19</v>
       </c>
       <c r="V11" t="s">
-        <v>1015</v>
+        <v>859</v>
       </c>
       <c r="W11" t="s">
-        <v>1016</v>
+        <v>860</v>
       </c>
       <c r="AF11" t="s">
-        <v>1017</v>
+        <v>861</v>
       </c>
       <c r="AG11">
         <v>10</v>
       </c>
       <c r="AH11" t="s">
-        <v>1018</v>
+        <v>862</v>
       </c>
     </row>
     <row r="12" spans="1:34">
       <c r="A12" s="2" t="s">
-        <v>1019</v>
+        <v>863</v>
       </c>
       <c r="B12" t="s">
         <v>63</v>
@@ -5661,57 +6063,57 @@
         <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>1020</v>
+        <v>864</v>
       </c>
       <c r="F12" t="s">
-        <v>1021</v>
+        <v>865</v>
       </c>
       <c r="G12" t="s">
-        <v>1022</v>
+        <v>866</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12" t="s">
-        <v>1023</v>
+        <v>867</v>
       </c>
       <c r="J12" t="s">
-        <v>1024</v>
+        <v>868</v>
       </c>
       <c r="K12" t="s">
         <v>42</v>
       </c>
       <c r="L12" t="s">
-        <v>1025</v>
+        <v>869</v>
       </c>
       <c r="Q12" t="s">
         <v>42</v>
       </c>
       <c r="R12" t="s">
-        <v>1026</v>
+        <v>870</v>
       </c>
       <c r="S12" t="s">
-        <v>1027</v>
+        <v>871</v>
       </c>
       <c r="T12" t="s">
-        <v>1028</v>
+        <v>872</v>
       </c>
       <c r="X12" t="s">
         <v>143</v>
       </c>
       <c r="Z12" t="s">
-        <v>1029</v>
+        <v>873</v>
       </c>
       <c r="AG12">
         <v>10</v>
       </c>
       <c r="AH12" t="s">
-        <v>1030</v>
+        <v>874</v>
       </c>
     </row>
     <row r="13" spans="1:34">
       <c r="A13" s="2" t="s">
-        <v>1031</v>
+        <v>875</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -5723,63 +6125,63 @@
         <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>1032</v>
+        <v>876</v>
       </c>
       <c r="F13" t="s">
-        <v>1033</v>
+        <v>877</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13" t="s">
-        <v>1034</v>
+        <v>878</v>
       </c>
       <c r="K13" t="s">
         <v>42</v>
       </c>
       <c r="L13" t="s">
-        <v>1035</v>
+        <v>879</v>
       </c>
       <c r="M13" t="s">
-        <v>1036</v>
+        <v>880</v>
       </c>
       <c r="Q13" t="s">
         <v>42</v>
       </c>
       <c r="R13" t="s">
-        <v>1037</v>
+        <v>881</v>
       </c>
       <c r="S13" t="s">
-        <v>1038</v>
+        <v>882</v>
       </c>
       <c r="T13" t="s">
-        <v>1039</v>
+        <v>883</v>
       </c>
       <c r="U13" t="s">
         <v>19</v>
       </c>
       <c r="V13" t="s">
-        <v>1040</v>
+        <v>884</v>
       </c>
       <c r="W13" t="s">
-        <v>1041</v>
+        <v>885</v>
       </c>
       <c r="AD13" t="s">
-        <v>1042</v>
+        <v>886</v>
       </c>
       <c r="AF13" t="s">
-        <v>1043</v>
+        <v>887</v>
       </c>
       <c r="AG13">
         <v>12</v>
       </c>
       <c r="AH13" t="s">
-        <v>1044</v>
+        <v>888</v>
       </c>
     </row>
     <row r="14" spans="1:34">
       <c r="A14" s="2" t="s">
-        <v>1045</v>
+        <v>889</v>
       </c>
       <c r="B14" t="s">
         <v>106</v>
@@ -5791,45 +6193,45 @@
         <v>42</v>
       </c>
       <c r="L14" t="s">
-        <v>1046</v>
+        <v>890</v>
       </c>
       <c r="M14" t="s">
-        <v>1047</v>
+        <v>891</v>
       </c>
       <c r="Q14" t="s">
         <v>42</v>
       </c>
       <c r="R14" t="s">
-        <v>1048</v>
+        <v>892</v>
       </c>
       <c r="S14" t="s">
-        <v>1049</v>
+        <v>893</v>
       </c>
       <c r="T14" t="s">
-        <v>1050</v>
+        <v>894</v>
       </c>
       <c r="U14" t="s">
         <v>19</v>
       </c>
       <c r="V14" t="s">
-        <v>1051</v>
+        <v>895</v>
       </c>
       <c r="W14" t="s">
-        <v>1052</v>
+        <v>896</v>
       </c>
       <c r="AF14" t="s">
-        <v>1053</v>
+        <v>897</v>
       </c>
       <c r="AG14">
         <v>8</v>
       </c>
       <c r="AH14" t="s">
-        <v>1054</v>
+        <v>898</v>
       </c>
     </row>
     <row r="15" spans="1:34">
       <c r="A15" s="2" t="s">
-        <v>1055</v>
+        <v>899</v>
       </c>
       <c r="B15" t="s">
         <v>63</v>
@@ -5841,36 +6243,36 @@
         <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>1056</v>
+        <v>900</v>
       </c>
       <c r="F15" t="s">
-        <v>1057</v>
+        <v>901</v>
       </c>
       <c r="K15" t="s">
         <v>42</v>
       </c>
       <c r="L15" t="s">
-        <v>1058</v>
+        <v>902</v>
       </c>
       <c r="Q15" t="s">
         <v>42</v>
       </c>
       <c r="R15" t="s">
-        <v>1059</v>
+        <v>903</v>
       </c>
       <c r="S15" t="s">
-        <v>1060</v>
+        <v>904</v>
       </c>
       <c r="AG15">
         <v>5</v>
       </c>
       <c r="AH15" t="s">
-        <v>1061</v>
+        <v>905</v>
       </c>
     </row>
     <row r="16" spans="1:34">
       <c r="A16" s="2" t="s">
-        <v>1062</v>
+        <v>906</v>
       </c>
       <c r="B16" t="s">
         <v>152</v>
@@ -5882,7 +6284,7 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>1063</v>
+        <v>907</v>
       </c>
     </row>
     <row r="17" spans="1:34">
@@ -6186,13 +6588,13 @@
         <v>118</v>
       </c>
       <c r="I21" t="s">
-        <v>1064</v>
+        <v>908</v>
       </c>
       <c r="J21" t="s">
-        <v>1065</v>
+        <v>909</v>
       </c>
       <c r="L21" t="s">
-        <v>1066</v>
+        <v>910</v>
       </c>
       <c r="M21" t="s">
         <v>125</v>
@@ -6204,13 +6606,13 @@
         <v>120</v>
       </c>
       <c r="T21" t="s">
-        <v>1067</v>
+        <v>911</v>
       </c>
       <c r="AC21" t="s">
-        <v>1068</v>
+        <v>912</v>
       </c>
       <c r="AD21" t="s">
-        <v>1069</v>
+        <v>913</v>
       </c>
     </row>
     <row r="22" spans="1:34">
@@ -6218,31 +6620,31 @@
         <v>126</v>
       </c>
       <c r="E22" t="s">
-        <v>1070</v>
+        <v>914</v>
       </c>
       <c r="F22" t="s">
-        <v>1071</v>
+        <v>915</v>
       </c>
       <c r="G22" t="s">
-        <v>1072</v>
+        <v>916</v>
       </c>
       <c r="J22" t="s">
-        <v>1073</v>
+        <v>917</v>
       </c>
       <c r="O22" t="s">
-        <v>1074</v>
+        <v>918</v>
       </c>
       <c r="R22" t="s">
-        <v>1075</v>
+        <v>919</v>
       </c>
       <c r="AA22" t="s">
-        <v>1076</v>
+        <v>920</v>
       </c>
       <c r="AB22" t="s">
-        <v>1077</v>
+        <v>921</v>
       </c>
       <c r="AD22" t="s">
-        <v>1078</v>
+        <v>922</v>
       </c>
     </row>
     <row r="23" spans="1:34">
@@ -6250,10 +6652,10 @@
         <v>130</v>
       </c>
       <c r="R23" t="s">
-        <v>1079</v>
+        <v>923</v>
       </c>
       <c r="AA23" t="s">
-        <v>1080</v>
+        <v>924</v>
       </c>
     </row>
     <row r="24" spans="1:34">
@@ -6261,7 +6663,7 @@
         <v>134</v>
       </c>
       <c r="AA24" t="s">
-        <v>1081</v>
+        <v>925</v>
       </c>
     </row>
     <row r="25" spans="1:34">
@@ -6355,20 +6757,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AC23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="29" width="35.33203125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="32.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:29">
       <c r="A1" s="5" t="s">
-        <v>1213</v>
+        <v>1057</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1082</v>
+        <v>926</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>385</v>
@@ -6383,7 +6782,7 @@
         <v>2</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>1083</v>
+        <v>927</v>
       </c>
       <c r="I1" s="3">
         <v>-114.086</v>
@@ -6395,7 +6794,7 @@
         <v>-112.08</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>1084</v>
+        <v>928</v>
       </c>
       <c r="M1" s="3">
         <v>-18.006</v>
@@ -6451,7 +6850,7 @@
     </row>
     <row r="2" spans="1:29">
       <c r="A2" s="3" t="s">
-        <v>1085</v>
+        <v>929</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
@@ -6463,12 +6862,12 @@
         <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>1086</v>
+        <v>930</v>
       </c>
     </row>
     <row r="3" spans="1:29">
       <c r="A3" s="3" t="s">
-        <v>1087</v>
+        <v>931</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -6480,12 +6879,12 @@
         <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>1088</v>
+        <v>932</v>
       </c>
     </row>
     <row r="4" spans="1:29">
       <c r="A4" s="3" t="s">
-        <v>1089</v>
+        <v>933</v>
       </c>
       <c r="B4" t="s">
         <v>188</v>
@@ -6494,18 +6893,18 @@
         <v>18</v>
       </c>
       <c r="P4" t="s">
-        <v>1090</v>
+        <v>934</v>
       </c>
       <c r="AB4">
         <v>1</v>
       </c>
       <c r="AC4" t="s">
-        <v>1091</v>
+        <v>935</v>
       </c>
     </row>
     <row r="5" spans="1:29">
       <c r="A5" s="3" t="s">
-        <v>1092</v>
+        <v>936</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -6517,36 +6916,36 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>1093</v>
+        <v>937</v>
       </c>
       <c r="F5" t="s">
-        <v>1094</v>
+        <v>938</v>
       </c>
       <c r="L5" t="s">
         <v>19</v>
       </c>
       <c r="M5" t="s">
-        <v>1095</v>
+        <v>939</v>
       </c>
       <c r="N5" t="s">
-        <v>1096</v>
+        <v>940</v>
       </c>
       <c r="Z5" t="s">
-        <v>1097</v>
+        <v>941</v>
       </c>
       <c r="AA5" t="s">
-        <v>1098</v>
+        <v>942</v>
       </c>
       <c r="AB5">
         <v>6</v>
       </c>
       <c r="AC5" t="s">
-        <v>1099</v>
+        <v>943</v>
       </c>
     </row>
     <row r="6" spans="1:29">
       <c r="A6" s="3" t="s">
-        <v>1100</v>
+        <v>944</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -6558,57 +6957,57 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>1101</v>
+        <v>945</v>
       </c>
       <c r="F6" t="s">
-        <v>1102</v>
+        <v>946</v>
       </c>
       <c r="G6" t="s">
-        <v>1103</v>
+        <v>947</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>1104</v>
+        <v>948</v>
       </c>
       <c r="J6" t="s">
-        <v>1105</v>
+        <v>949</v>
       </c>
       <c r="K6" t="s">
-        <v>1106</v>
+        <v>950</v>
       </c>
       <c r="L6" t="s">
         <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>1107</v>
+        <v>951</v>
       </c>
       <c r="N6" t="s">
-        <v>1108</v>
+        <v>952</v>
       </c>
       <c r="P6" t="s">
-        <v>1109</v>
+        <v>953</v>
       </c>
       <c r="U6" t="s">
-        <v>1110</v>
+        <v>954</v>
       </c>
       <c r="Z6" t="s">
-        <v>1111</v>
+        <v>955</v>
       </c>
       <c r="AA6" t="s">
-        <v>1112</v>
+        <v>956</v>
       </c>
       <c r="AB6">
         <v>13</v>
       </c>
       <c r="AC6" t="s">
-        <v>1113</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7" spans="1:29">
       <c r="A7" s="3" t="s">
-        <v>1114</v>
+        <v>958</v>
       </c>
       <c r="B7" t="s">
         <v>106</v>
@@ -6620,66 +7019,66 @@
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>1115</v>
+        <v>959</v>
       </c>
       <c r="F7" t="s">
-        <v>1116</v>
+        <v>960</v>
       </c>
       <c r="G7" t="s">
-        <v>1117</v>
+        <v>961</v>
       </c>
       <c r="H7" t="s">
         <v>42</v>
       </c>
       <c r="I7" t="s">
-        <v>1118</v>
+        <v>962</v>
       </c>
       <c r="J7" t="s">
-        <v>1119</v>
+        <v>963</v>
       </c>
       <c r="K7" t="s">
-        <v>1120</v>
+        <v>964</v>
       </c>
       <c r="L7" t="s">
         <v>19</v>
       </c>
       <c r="M7" t="s">
-        <v>1121</v>
+        <v>965</v>
       </c>
       <c r="N7" t="s">
-        <v>1122</v>
+        <v>966</v>
       </c>
       <c r="O7" t="s">
-        <v>1123</v>
+        <v>967</v>
       </c>
       <c r="P7" t="s">
-        <v>1124</v>
+        <v>968</v>
       </c>
       <c r="Q7" t="s">
-        <v>1125</v>
+        <v>969</v>
       </c>
       <c r="U7" t="s">
-        <v>1126</v>
+        <v>970</v>
       </c>
       <c r="V7" t="s">
-        <v>1127</v>
+        <v>971</v>
       </c>
       <c r="X7" t="s">
-        <v>1128</v>
+        <v>972</v>
       </c>
       <c r="Y7" t="s">
-        <v>1129</v>
+        <v>973</v>
       </c>
       <c r="AB7">
         <v>15</v>
       </c>
       <c r="AC7" t="s">
-        <v>1130</v>
+        <v>974</v>
       </c>
     </row>
     <row r="8" spans="1:29">
       <c r="A8" s="3" t="s">
-        <v>1131</v>
+        <v>975</v>
       </c>
       <c r="B8" t="s">
         <v>188</v>
@@ -6691,45 +7090,45 @@
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>1132</v>
+        <v>976</v>
       </c>
       <c r="F8" t="s">
-        <v>1133</v>
+        <v>977</v>
       </c>
       <c r="G8" t="s">
-        <v>1134</v>
+        <v>978</v>
       </c>
       <c r="L8" t="s">
         <v>19</v>
       </c>
       <c r="M8" t="s">
-        <v>1135</v>
+        <v>979</v>
       </c>
       <c r="Q8" t="s">
-        <v>1136</v>
+        <v>980</v>
       </c>
       <c r="U8" t="s">
-        <v>1137</v>
+        <v>981</v>
       </c>
       <c r="W8" t="s">
-        <v>1138</v>
+        <v>982</v>
       </c>
       <c r="X8" t="s">
-        <v>1139</v>
+        <v>983</v>
       </c>
       <c r="AA8" t="s">
-        <v>1140</v>
+        <v>984</v>
       </c>
       <c r="AB8">
         <v>9</v>
       </c>
       <c r="AC8" t="s">
-        <v>1141</v>
+        <v>985</v>
       </c>
     </row>
     <row r="9" spans="1:29">
       <c r="A9" s="3" t="s">
-        <v>1142</v>
+        <v>986</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -6741,51 +7140,51 @@
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>1143</v>
+        <v>987</v>
       </c>
       <c r="F9" t="s">
-        <v>1144</v>
+        <v>988</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
       </c>
       <c r="I9" t="s">
-        <v>1145</v>
+        <v>989</v>
       </c>
       <c r="J9" t="s">
-        <v>1146</v>
+        <v>990</v>
       </c>
       <c r="K9" t="s">
-        <v>1147</v>
+        <v>991</v>
       </c>
       <c r="L9" t="s">
         <v>19</v>
       </c>
       <c r="M9" t="s">
-        <v>1148</v>
+        <v>992</v>
       </c>
       <c r="N9" t="s">
-        <v>1149</v>
+        <v>993</v>
       </c>
       <c r="O9" t="s">
-        <v>1150</v>
+        <v>994</v>
       </c>
       <c r="U9" t="s">
-        <v>1151</v>
+        <v>995</v>
       </c>
       <c r="V9" t="s">
-        <v>1152</v>
+        <v>996</v>
       </c>
       <c r="AB9">
         <v>10</v>
       </c>
       <c r="AC9" t="s">
-        <v>1153</v>
+        <v>997</v>
       </c>
     </row>
     <row r="10" spans="1:29">
       <c r="A10" s="3" t="s">
-        <v>1154</v>
+        <v>998</v>
       </c>
       <c r="B10" t="s">
         <v>106</v>
@@ -6797,42 +7196,42 @@
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>1155</v>
+        <v>999</v>
       </c>
       <c r="F10" t="s">
-        <v>1156</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
       </c>
       <c r="I10" t="s">
-        <v>1157</v>
+        <v>1001</v>
       </c>
       <c r="J10" t="s">
-        <v>1158</v>
+        <v>1002</v>
       </c>
       <c r="K10" t="s">
-        <v>1159</v>
+        <v>1003</v>
       </c>
       <c r="L10" t="s">
         <v>143</v>
       </c>
       <c r="N10" t="s">
-        <v>1160</v>
+        <v>1004</v>
       </c>
       <c r="O10" t="s">
-        <v>1161</v>
+        <v>1005</v>
       </c>
       <c r="AB10">
         <v>7</v>
       </c>
       <c r="AC10" t="s">
-        <v>1162</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="11" spans="1:29">
       <c r="A11" s="3" t="s">
-        <v>1163</v>
+        <v>1007</v>
       </c>
       <c r="B11" t="s">
         <v>58</v>
@@ -6844,27 +7243,27 @@
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>1164</v>
+        <v>1008</v>
       </c>
       <c r="F11" t="s">
-        <v>1165</v>
+        <v>1009</v>
       </c>
       <c r="G11" t="s">
-        <v>1166</v>
+        <v>1010</v>
       </c>
       <c r="R11" t="s">
-        <v>1167</v>
+        <v>1011</v>
       </c>
       <c r="AB11">
         <v>4</v>
       </c>
       <c r="AC11" t="s">
-        <v>1168</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="12" spans="1:29">
       <c r="A12" s="3" t="s">
-        <v>1169</v>
+        <v>1013</v>
       </c>
       <c r="B12" t="s">
         <v>58</v>
@@ -6876,45 +7275,45 @@
         <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>1170</v>
+        <v>1014</v>
       </c>
       <c r="F12" t="s">
-        <v>1171</v>
+        <v>1015</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>1172</v>
+        <v>1016</v>
       </c>
       <c r="J12" t="s">
-        <v>1173</v>
+        <v>1017</v>
       </c>
       <c r="K12" t="s">
-        <v>1174</v>
+        <v>1018</v>
       </c>
       <c r="L12" t="s">
-        <v>1175</v>
+        <v>1019</v>
       </c>
       <c r="M12" t="s">
-        <v>1176</v>
+        <v>1020</v>
       </c>
       <c r="N12" t="s">
-        <v>1177</v>
+        <v>1021</v>
       </c>
       <c r="V12" t="s">
-        <v>1178</v>
+        <v>1022</v>
       </c>
       <c r="AB12">
         <v>8</v>
       </c>
       <c r="AC12" t="s">
-        <v>1179</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="13" spans="1:29">
       <c r="A13" s="3" t="s">
-        <v>1180</v>
+        <v>1024</v>
       </c>
       <c r="B13" t="s">
         <v>38</v>
@@ -6926,48 +7325,48 @@
         <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>1181</v>
+        <v>1025</v>
       </c>
       <c r="F13" t="s">
-        <v>1182</v>
+        <v>1026</v>
       </c>
       <c r="G13" t="s">
-        <v>1183</v>
+        <v>1027</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
       </c>
       <c r="I13" t="s">
-        <v>1184</v>
+        <v>1028</v>
       </c>
       <c r="J13" t="s">
-        <v>1185</v>
+        <v>1029</v>
       </c>
       <c r="K13" t="s">
-        <v>1186</v>
+        <v>1030</v>
       </c>
       <c r="L13" t="s">
         <v>19</v>
       </c>
       <c r="M13" t="s">
-        <v>1187</v>
+        <v>1031</v>
       </c>
       <c r="N13" t="s">
-        <v>1188</v>
+        <v>1032</v>
       </c>
       <c r="AA13" t="s">
-        <v>1189</v>
+        <v>1033</v>
       </c>
       <c r="AB13">
         <v>9</v>
       </c>
       <c r="AC13" t="s">
-        <v>1190</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="14" spans="1:29">
       <c r="A14" s="3" t="s">
-        <v>1191</v>
+        <v>1035</v>
       </c>
       <c r="B14" t="s">
         <v>106</v>
@@ -6979,7 +7378,7 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>1192</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -7271,13 +7670,13 @@
         <v>118</v>
       </c>
       <c r="Q19" t="s">
-        <v>1193</v>
+        <v>1037</v>
       </c>
       <c r="U19" t="s">
-        <v>1194</v>
+        <v>1038</v>
       </c>
       <c r="V19" t="s">
-        <v>1195</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -7285,31 +7684,31 @@
         <v>126</v>
       </c>
       <c r="E20" t="s">
-        <v>1196</v>
+        <v>1040</v>
       </c>
       <c r="O20" t="s">
-        <v>1197</v>
+        <v>1041</v>
       </c>
       <c r="Q20" t="s">
-        <v>1198</v>
+        <v>1042</v>
       </c>
       <c r="R20" t="s">
-        <v>1199</v>
+        <v>1043</v>
       </c>
       <c r="S20" t="s">
-        <v>1200</v>
+        <v>1044</v>
       </c>
       <c r="X20" t="s">
-        <v>1201</v>
+        <v>1045</v>
       </c>
       <c r="Y20" t="s">
-        <v>1202</v>
+        <v>1046</v>
       </c>
       <c r="Z20" t="s">
-        <v>1203</v>
+        <v>1047</v>
       </c>
       <c r="AA20" t="s">
-        <v>1204</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -7317,13 +7716,13 @@
         <v>130</v>
       </c>
       <c r="R21" t="s">
-        <v>1205</v>
+        <v>1049</v>
       </c>
       <c r="S21" t="s">
-        <v>1206</v>
+        <v>1050</v>
       </c>
       <c r="Z21" t="s">
-        <v>1207</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -7331,10 +7730,10 @@
         <v>134</v>
       </c>
       <c r="R22" t="s">
-        <v>1208</v>
+        <v>1052</v>
       </c>
       <c r="S22" t="s">
-        <v>1209</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -7425,10 +7824,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AF42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="32" width="37.83203125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="32.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
@@ -9131,95 +9527,95 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AA162"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB9E97F-CCC1-2741-B29F-3488A5D8FBC3}">
+  <dimension ref="A1:AA171"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="32.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="5" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2">
+      <c r="F1" s="5">
         <v>1</v>
       </c>
-      <c r="G1" s="2">
+      <c r="G1" s="5">
         <v>2</v>
       </c>
-      <c r="H1" s="2">
+      <c r="H1" s="5">
         <v>3</v>
       </c>
-      <c r="I1" s="2">
+      <c r="I1" s="5">
         <v>4</v>
       </c>
-      <c r="J1" s="2">
+      <c r="J1" s="5">
         <v>5</v>
       </c>
-      <c r="K1" s="2">
+      <c r="K1" s="5">
         <v>6</v>
       </c>
-      <c r="L1" s="2">
+      <c r="L1" s="5">
         <v>7</v>
       </c>
-      <c r="M1" s="2">
+      <c r="M1" s="5">
         <v>8</v>
       </c>
-      <c r="N1" s="2">
+      <c r="N1" s="5">
         <v>9</v>
       </c>
-      <c r="O1" s="2">
+      <c r="O1" s="5">
         <v>10</v>
       </c>
-      <c r="P1" s="2">
+      <c r="P1" s="5">
         <v>11</v>
       </c>
-      <c r="Q1" s="2">
+      <c r="Q1" s="5">
         <v>12</v>
       </c>
-      <c r="R1" s="2">
+      <c r="R1" s="5">
         <v>13</v>
       </c>
-      <c r="S1" s="2">
+      <c r="S1" s="5">
         <v>14</v>
       </c>
-      <c r="T1" s="2">
+      <c r="T1" s="5">
         <v>15</v>
       </c>
-      <c r="U1" s="2">
+      <c r="U1" s="5">
         <v>16</v>
       </c>
-      <c r="V1" s="2">
+      <c r="V1" s="5">
         <v>17</v>
       </c>
-      <c r="W1" s="2">
+      <c r="W1" s="5">
         <v>18</v>
       </c>
-      <c r="X1" s="2">
+      <c r="X1" s="5">
         <v>19</v>
       </c>
-      <c r="Y1" s="2">
+      <c r="Y1" s="5">
         <v>20</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
         <v>386</v>
       </c>
       <c r="B2" t="s">
@@ -9236,7 +9632,7 @@
       </c>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="5" t="s">
         <v>388</v>
       </c>
       <c r="B3" t="s">
@@ -9253,7 +9649,7 @@
       </c>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="5" t="s">
         <v>390</v>
       </c>
       <c r="B4" t="s">
@@ -9270,7 +9666,7 @@
       </c>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="5" t="s">
         <v>392</v>
       </c>
       <c r="B5" t="s">
@@ -9287,7 +9683,7 @@
       </c>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="5" t="s">
         <v>394</v>
       </c>
       <c r="B6" t="s">
@@ -9304,7 +9700,7 @@
       </c>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="5" t="s">
         <v>396</v>
       </c>
       <c r="B7" t="s">
@@ -9321,7 +9717,7 @@
       </c>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="5" t="s">
         <v>398</v>
       </c>
       <c r="B8" t="s">
@@ -9336,37 +9732,16 @@
       <c r="G8" t="s">
         <v>400</v>
       </c>
-      <c r="H8" t="s">
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="s">
         <v>401</v>
       </c>
-      <c r="K8" t="s">
+    </row>
+    <row r="9" spans="1:27">
+      <c r="A9" s="5" t="s">
         <v>402</v>
-      </c>
-      <c r="N8" t="s">
-        <v>403</v>
-      </c>
-      <c r="O8" t="s">
-        <v>404</v>
-      </c>
-      <c r="P8" t="s">
-        <v>405</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>406</v>
-      </c>
-      <c r="R8" t="s">
-        <v>407</v>
-      </c>
-      <c r="Z8">
-        <v>8</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27">
-      <c r="A9" s="2" t="s">
-        <v>409</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
@@ -9375,30 +9750,33 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="K9" t="s">
-        <v>411</v>
+        <v>404</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1285</v>
       </c>
       <c r="R9" t="s">
-        <v>412</v>
-      </c>
-      <c r="T9" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="U9" t="s">
-        <v>414</v>
+        <v>1284</v>
+      </c>
+      <c r="W9" t="s">
+        <v>1283</v>
       </c>
       <c r="Z9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10" s="2" t="s">
-        <v>416</v>
+      <c r="A10" s="5" t="s">
+        <v>407</v>
       </c>
       <c r="B10" t="s">
         <v>79</v>
@@ -9410,35 +9788,29 @@
         <v>0</v>
       </c>
       <c r="AA10" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:27">
-      <c r="A11" s="2" t="s">
-        <v>418</v>
+      <c r="A11" s="5" t="s">
+        <v>409</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" t="s">
-        <v>419</v>
-      </c>
-      <c r="U11" t="s">
-        <v>420</v>
+        <v>140</v>
       </c>
       <c r="Z11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="2" t="s">
-        <v>422</v>
+      <c r="A12" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="B12" t="s">
         <v>106</v>
@@ -9450,12 +9822,12 @@
         <v>0</v>
       </c>
       <c r="AA12" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="2" t="s">
-        <v>424</v>
+      <c r="A13" s="5" t="s">
+        <v>413</v>
       </c>
       <c r="B13" t="s">
         <v>181</v>
@@ -9467,12 +9839,12 @@
         <v>0</v>
       </c>
       <c r="AA13" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
     </row>
     <row r="14" spans="1:27">
-      <c r="A14" s="2" t="s">
-        <v>426</v>
+      <c r="A14" s="5" t="s">
+        <v>415</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -9484,12 +9856,12 @@
         <v>0</v>
       </c>
       <c r="AA14" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" spans="1:27">
-      <c r="A15" s="2" t="s">
-        <v>428</v>
+      <c r="A15" s="5" t="s">
+        <v>417</v>
       </c>
       <c r="B15" t="s">
         <v>280</v>
@@ -9501,12 +9873,12 @@
         <v>0</v>
       </c>
       <c r="AA15" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
     </row>
     <row r="16" spans="1:27">
-      <c r="A16" s="2" t="s">
-        <v>430</v>
+      <c r="A16" s="5" t="s">
+        <v>419</v>
       </c>
       <c r="B16" t="s">
         <v>58</v>
@@ -9518,12 +9890,12 @@
         <v>0</v>
       </c>
       <c r="AA16" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
     </row>
     <row r="17" spans="1:27">
-      <c r="A17" s="2" t="s">
-        <v>432</v>
+      <c r="A17" s="5" t="s">
+        <v>421</v>
       </c>
       <c r="B17" t="s">
         <v>346</v>
@@ -9532,24 +9904,24 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="K17" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="X17" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="Z17">
         <v>2</v>
       </c>
       <c r="AA17" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="2" t="s">
-        <v>436</v>
+      <c r="A18" s="5" t="s">
+        <v>425</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
@@ -9561,12 +9933,12 @@
         <v>0</v>
       </c>
       <c r="AA18" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
     </row>
     <row r="19" spans="1:27">
-      <c r="A19" s="2" t="s">
-        <v>438</v>
+      <c r="A19" s="5" t="s">
+        <v>427</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -9578,12 +9950,12 @@
         <v>0</v>
       </c>
       <c r="AA19" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="2" t="s">
-        <v>440</v>
+      <c r="A20" s="5" t="s">
+        <v>429</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
@@ -9595,50 +9967,29 @@
         <v>0</v>
       </c>
       <c r="AA20" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
     </row>
     <row r="21" spans="1:27">
-      <c r="A21" s="2" t="s">
-        <v>442</v>
+      <c r="A21" s="5" t="s">
+        <v>431</v>
       </c>
       <c r="B21" t="s">
         <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" t="s">
-        <v>443</v>
-      </c>
-      <c r="J21" t="s">
-        <v>444</v>
-      </c>
-      <c r="K21" t="s">
-        <v>445</v>
-      </c>
-      <c r="L21" t="s">
-        <v>446</v>
-      </c>
-      <c r="M21" t="s">
-        <v>447</v>
-      </c>
-      <c r="N21" t="s">
-        <v>448</v>
-      </c>
-      <c r="O21" t="s">
-        <v>449</v>
+        <v>140</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" spans="1:27">
-      <c r="A22" s="2" t="s">
-        <v>451</v>
+      <c r="A22" s="5" t="s">
+        <v>433</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
@@ -9650,12 +10001,12 @@
         <v>0</v>
       </c>
       <c r="AA22" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
     </row>
     <row r="23" spans="1:27">
-      <c r="A23" s="2" t="s">
-        <v>453</v>
+      <c r="A23" s="5" t="s">
+        <v>435</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -9667,12 +10018,12 @@
         <v>0</v>
       </c>
       <c r="AA23" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
     </row>
     <row r="24" spans="1:27">
-      <c r="A24" s="2" t="s">
-        <v>455</v>
+      <c r="A24" s="5" t="s">
+        <v>437</v>
       </c>
       <c r="B24" t="s">
         <v>58</v>
@@ -9684,12 +10035,12 @@
         <v>0</v>
       </c>
       <c r="AA24" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
     </row>
     <row r="25" spans="1:27">
-      <c r="A25" s="2" t="s">
-        <v>457</v>
+      <c r="A25" s="5" t="s">
+        <v>439</v>
       </c>
       <c r="B25" t="s">
         <v>63</v>
@@ -9698,21 +10049,21 @@
         <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="R25" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="Z25">
         <v>1</v>
       </c>
       <c r="AA25" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
     </row>
     <row r="26" spans="1:27">
-      <c r="A26" s="2" t="s">
-        <v>461</v>
+      <c r="A26" s="5" t="s">
+        <v>443</v>
       </c>
       <c r="B26" t="s">
         <v>58</v>
@@ -9721,38 +10072,50 @@
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="N26" t="s">
-        <v>463</v>
+        <v>445</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>1282</v>
       </c>
       <c r="Z26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
     </row>
     <row r="27" spans="1:27">
-      <c r="A27" s="2" t="s">
-        <v>465</v>
+      <c r="A27" s="5" t="s">
+        <v>447</v>
       </c>
       <c r="B27" t="s">
         <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>140</v>
+        <v>18</v>
+      </c>
+      <c r="D27" t="s">
+        <v>403</v>
+      </c>
+      <c r="K27" t="s">
+        <v>1281</v>
+      </c>
+      <c r="R27" t="s">
+        <v>1280</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
     </row>
     <row r="28" spans="1:27">
-      <c r="A28" s="2" t="s">
-        <v>467</v>
+      <c r="A28" s="5" t="s">
+        <v>449</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -9764,12 +10127,12 @@
         <v>0</v>
       </c>
       <c r="AA28" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
     </row>
     <row r="29" spans="1:27">
-      <c r="A29" s="2" t="s">
-        <v>469</v>
+      <c r="A29" s="5" t="s">
+        <v>451</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
@@ -9781,12 +10144,12 @@
         <v>0</v>
       </c>
       <c r="AA29" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
     </row>
     <row r="30" spans="1:27">
-      <c r="A30" s="2" t="s">
-        <v>471</v>
+      <c r="A30" s="5" t="s">
+        <v>453</v>
       </c>
       <c r="B30" t="s">
         <v>106</v>
@@ -9798,12 +10161,12 @@
         <v>0</v>
       </c>
       <c r="AA30" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
     </row>
     <row r="31" spans="1:27">
-      <c r="A31" s="2" t="s">
-        <v>473</v>
+      <c r="A31" s="5" t="s">
+        <v>455</v>
       </c>
       <c r="B31" t="s">
         <v>38</v>
@@ -9815,12 +10178,12 @@
         <v>0</v>
       </c>
       <c r="AA31" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
     </row>
     <row r="32" spans="1:27">
-      <c r="A32" s="2" t="s">
-        <v>475</v>
+      <c r="A32" s="5" t="s">
+        <v>457</v>
       </c>
       <c r="B32" t="s">
         <v>114</v>
@@ -9832,12 +10195,12 @@
         <v>0</v>
       </c>
       <c r="AA32" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="33" spans="1:27">
-      <c r="A33" s="2" t="s">
-        <v>477</v>
+      <c r="A33" s="5" t="s">
+        <v>459</v>
       </c>
       <c r="B33" t="s">
         <v>106</v>
@@ -9849,12 +10212,12 @@
         <v>0</v>
       </c>
       <c r="AA33" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
     </row>
     <row r="34" spans="1:27">
-      <c r="A34" s="2" t="s">
-        <v>479</v>
+      <c r="A34" s="5" t="s">
+        <v>461</v>
       </c>
       <c r="B34" t="s">
         <v>155</v>
@@ -9866,29 +10229,35 @@
         <v>0</v>
       </c>
       <c r="AA34" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
     </row>
     <row r="35" spans="1:27">
-      <c r="A35" s="2" t="s">
-        <v>481</v>
+      <c r="A35" s="5" t="s">
+        <v>463</v>
       </c>
       <c r="B35" t="s">
         <v>188</v>
       </c>
       <c r="C35" t="s">
-        <v>140</v>
+        <v>18</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1279</v>
+      </c>
+      <c r="U35" t="s">
+        <v>1278</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
     </row>
     <row r="36" spans="1:27">
-      <c r="A36" s="2" t="s">
-        <v>483</v>
+      <c r="A36" s="5" t="s">
+        <v>465</v>
       </c>
       <c r="B36" t="s">
         <v>58</v>
@@ -9900,12 +10269,12 @@
         <v>0</v>
       </c>
       <c r="AA36" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
     </row>
     <row r="37" spans="1:27">
-      <c r="A37" s="2" t="s">
-        <v>485</v>
+      <c r="A37" s="5" t="s">
+        <v>467</v>
       </c>
       <c r="B37" t="s">
         <v>63</v>
@@ -9914,39 +10283,27 @@
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>486</v>
+        <v>1277</v>
       </c>
       <c r="L37" t="s">
-        <v>487</v>
-      </c>
-      <c r="M37" t="s">
-        <v>488</v>
+        <v>1276</v>
       </c>
       <c r="N37" t="s">
-        <v>489</v>
-      </c>
-      <c r="O37" t="s">
-        <v>490</v>
-      </c>
-      <c r="P37" t="s">
-        <v>491</v>
-      </c>
-      <c r="R37" t="s">
-        <v>492</v>
+        <v>468</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA37" t="s">
-        <v>493</v>
+        <v>469</v>
       </c>
     </row>
     <row r="38" spans="1:27">
-      <c r="A38" s="2" t="s">
-        <v>494</v>
+      <c r="A38" s="5" t="s">
+        <v>470</v>
       </c>
       <c r="B38" t="s">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="C38" t="s">
         <v>140</v>
@@ -9955,12 +10312,12 @@
         <v>0</v>
       </c>
       <c r="AA38" t="s">
-        <v>496</v>
+        <v>472</v>
       </c>
     </row>
     <row r="39" spans="1:27">
-      <c r="A39" s="2" t="s">
-        <v>497</v>
+      <c r="A39" s="5" t="s">
+        <v>473</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
@@ -9972,12 +10329,12 @@
         <v>0</v>
       </c>
       <c r="AA39" t="s">
-        <v>498</v>
+        <v>474</v>
       </c>
     </row>
     <row r="40" spans="1:27">
-      <c r="A40" s="2" t="s">
-        <v>499</v>
+      <c r="A40" s="5" t="s">
+        <v>475</v>
       </c>
       <c r="B40" t="s">
         <v>188</v>
@@ -9989,12 +10346,12 @@
         <v>0</v>
       </c>
       <c r="AA40" t="s">
-        <v>500</v>
+        <v>476</v>
       </c>
     </row>
     <row r="41" spans="1:27">
-      <c r="A41" s="2" t="s">
-        <v>501</v>
+      <c r="A41" s="5" t="s">
+        <v>477</v>
       </c>
       <c r="B41" t="s">
         <v>106</v>
@@ -10006,12 +10363,12 @@
         <v>0</v>
       </c>
       <c r="AA41" t="s">
-        <v>502</v>
+        <v>478</v>
       </c>
     </row>
     <row r="42" spans="1:27">
-      <c r="A42" s="2" t="s">
-        <v>503</v>
+      <c r="A42" s="5" t="s">
+        <v>479</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -10023,12 +10380,12 @@
         <v>0</v>
       </c>
       <c r="AA42" t="s">
-        <v>504</v>
+        <v>480</v>
       </c>
     </row>
     <row r="43" spans="1:27">
-      <c r="A43" s="2" t="s">
-        <v>505</v>
+      <c r="A43" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="B43" t="s">
         <v>346</v>
@@ -10037,21 +10394,21 @@
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="J43" t="s">
-        <v>507</v>
+        <v>483</v>
       </c>
       <c r="Z43">
         <v>1</v>
       </c>
       <c r="AA43" t="s">
-        <v>508</v>
+        <v>484</v>
       </c>
     </row>
     <row r="44" spans="1:27">
-      <c r="A44" s="2" t="s">
-        <v>509</v>
+      <c r="A44" s="5" t="s">
+        <v>485</v>
       </c>
       <c r="B44" t="s">
         <v>155</v>
@@ -10063,44 +10420,29 @@
         <v>0</v>
       </c>
       <c r="AA44" t="s">
-        <v>510</v>
+        <v>486</v>
       </c>
     </row>
     <row r="45" spans="1:27">
-      <c r="A45" s="2" t="s">
-        <v>511</v>
+      <c r="A45" s="5" t="s">
+        <v>487</v>
       </c>
       <c r="B45" t="s">
         <v>28</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
-      </c>
-      <c r="D45" t="s">
-        <v>512</v>
-      </c>
-      <c r="M45" t="s">
-        <v>513</v>
-      </c>
-      <c r="N45" t="s">
-        <v>514</v>
-      </c>
-      <c r="O45" t="s">
-        <v>515</v>
-      </c>
-      <c r="P45" t="s">
-        <v>516</v>
+        <v>140</v>
       </c>
       <c r="Z45">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="s">
-        <v>517</v>
+        <v>489</v>
       </c>
     </row>
     <row r="46" spans="1:27">
-      <c r="A46" s="2" t="s">
-        <v>518</v>
+      <c r="A46" s="5" t="s">
+        <v>490</v>
       </c>
       <c r="B46" t="s">
         <v>346</v>
@@ -10112,12 +10454,12 @@
         <v>0</v>
       </c>
       <c r="AA46" t="s">
-        <v>519</v>
+        <v>491</v>
       </c>
     </row>
     <row r="47" spans="1:27">
-      <c r="A47" s="2" t="s">
-        <v>520</v>
+      <c r="A47" s="5" t="s">
+        <v>492</v>
       </c>
       <c r="B47" t="s">
         <v>155</v>
@@ -10129,12 +10471,12 @@
         <v>0</v>
       </c>
       <c r="AA47" t="s">
-        <v>521</v>
+        <v>493</v>
       </c>
     </row>
     <row r="48" spans="1:27">
-      <c r="A48" s="2" t="s">
-        <v>522</v>
+      <c r="A48" s="5" t="s">
+        <v>494</v>
       </c>
       <c r="B48" t="s">
         <v>346</v>
@@ -10143,27 +10485,21 @@
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>523</v>
-      </c>
-      <c r="K48" t="s">
-        <v>524</v>
-      </c>
-      <c r="L48" t="s">
-        <v>525</v>
+        <v>1275</v>
       </c>
       <c r="R48" t="s">
-        <v>526</v>
+        <v>495</v>
       </c>
       <c r="Z48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA48" t="s">
-        <v>527</v>
+        <v>496</v>
       </c>
     </row>
     <row r="49" spans="1:27">
-      <c r="A49" s="2" t="s">
-        <v>528</v>
+      <c r="A49" s="5" t="s">
+        <v>497</v>
       </c>
       <c r="B49" t="s">
         <v>63</v>
@@ -10175,12 +10511,12 @@
         <v>0</v>
       </c>
       <c r="AA49" t="s">
-        <v>529</v>
+        <v>498</v>
       </c>
     </row>
     <row r="50" spans="1:27">
-      <c r="A50" s="2" t="s">
-        <v>530</v>
+      <c r="A50" s="5" t="s">
+        <v>499</v>
       </c>
       <c r="B50" t="s">
         <v>106</v>
@@ -10192,12 +10528,12 @@
         <v>0</v>
       </c>
       <c r="AA50" t="s">
-        <v>531</v>
+        <v>500</v>
       </c>
     </row>
     <row r="51" spans="1:27">
-      <c r="A51" s="2" t="s">
-        <v>532</v>
+      <c r="A51" s="5" t="s">
+        <v>501</v>
       </c>
       <c r="B51" t="s">
         <v>346</v>
@@ -10209,12 +10545,12 @@
         <v>0</v>
       </c>
       <c r="AA51" t="s">
-        <v>533</v>
+        <v>502</v>
       </c>
     </row>
     <row r="52" spans="1:27">
-      <c r="A52" s="2" t="s">
-        <v>534</v>
+      <c r="A52" s="5" t="s">
+        <v>503</v>
       </c>
       <c r="B52" t="s">
         <v>188</v>
@@ -10223,44 +10559,38 @@
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>535</v>
+        <v>504</v>
       </c>
       <c r="M52" t="s">
-        <v>536</v>
+        <v>505</v>
       </c>
       <c r="Z52">
         <v>1</v>
       </c>
       <c r="AA52" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
     </row>
     <row r="53" spans="1:27">
-      <c r="A53" s="2" t="s">
-        <v>538</v>
+      <c r="A53" s="5" t="s">
+        <v>507</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
       </c>
       <c r="C53" t="s">
-        <v>18</v>
-      </c>
-      <c r="D53" t="s">
-        <v>539</v>
-      </c>
-      <c r="P53" t="s">
-        <v>540</v>
+        <v>140</v>
       </c>
       <c r="Z53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="s">
-        <v>541</v>
+        <v>508</v>
       </c>
     </row>
     <row r="54" spans="1:27">
-      <c r="A54" s="2" t="s">
-        <v>542</v>
+      <c r="A54" s="5" t="s">
+        <v>509</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
@@ -10272,12 +10602,12 @@
         <v>0</v>
       </c>
       <c r="AA54" t="s">
-        <v>543</v>
+        <v>510</v>
       </c>
     </row>
     <row r="55" spans="1:27">
-      <c r="A55" s="2" t="s">
-        <v>544</v>
+      <c r="A55" s="5" t="s">
+        <v>511</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
@@ -10286,51 +10616,27 @@
         <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>506</v>
-      </c>
-      <c r="J55" t="s">
-        <v>545</v>
-      </c>
-      <c r="K55" t="s">
-        <v>546</v>
-      </c>
-      <c r="L55" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="M55" t="s">
-        <v>548</v>
-      </c>
-      <c r="N55" t="s">
-        <v>549</v>
-      </c>
-      <c r="O55" t="s">
-        <v>550</v>
-      </c>
-      <c r="P55" t="s">
-        <v>551</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>552</v>
-      </c>
-      <c r="R55" t="s">
-        <v>553</v>
+        <v>512</v>
       </c>
       <c r="S55" t="s">
-        <v>554</v>
+        <v>1274</v>
       </c>
       <c r="T55" t="s">
-        <v>555</v>
+        <v>513</v>
       </c>
       <c r="Z55">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AA55" t="s">
-        <v>556</v>
+        <v>514</v>
       </c>
     </row>
     <row r="56" spans="1:27">
-      <c r="A56" s="2" t="s">
-        <v>557</v>
+      <c r="A56" s="5" t="s">
+        <v>515</v>
       </c>
       <c r="B56" t="s">
         <v>172</v>
@@ -10339,44 +10645,38 @@
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>558</v>
+        <v>516</v>
       </c>
       <c r="J56" t="s">
-        <v>559</v>
+        <v>517</v>
       </c>
       <c r="Z56">
         <v>1</v>
       </c>
       <c r="AA56" t="s">
-        <v>560</v>
+        <v>518</v>
       </c>
     </row>
     <row r="57" spans="1:27">
-      <c r="A57" s="2" t="s">
-        <v>561</v>
+      <c r="A57" s="5" t="s">
+        <v>519</v>
       </c>
       <c r="B57" t="s">
         <v>346</v>
       </c>
       <c r="C57" t="s">
-        <v>18</v>
-      </c>
-      <c r="D57" t="s">
-        <v>562</v>
-      </c>
-      <c r="L57" t="s">
-        <v>563</v>
+        <v>140</v>
       </c>
       <c r="Z57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="s">
-        <v>564</v>
+        <v>521</v>
       </c>
     </row>
     <row r="58" spans="1:27">
-      <c r="A58" s="2" t="s">
-        <v>565</v>
+      <c r="A58" s="5" t="s">
+        <v>522</v>
       </c>
       <c r="B58" t="s">
         <v>17</v>
@@ -10388,12 +10688,12 @@
         <v>0</v>
       </c>
       <c r="AA58" t="s">
-        <v>566</v>
+        <v>523</v>
       </c>
     </row>
     <row r="59" spans="1:27">
-      <c r="A59" s="2" t="s">
-        <v>567</v>
+      <c r="A59" s="5" t="s">
+        <v>524</v>
       </c>
       <c r="B59" t="s">
         <v>152</v>
@@ -10402,21 +10702,21 @@
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>512</v>
+        <v>488</v>
       </c>
       <c r="M59" t="s">
-        <v>568</v>
+        <v>525</v>
       </c>
       <c r="Z59">
         <v>1</v>
       </c>
       <c r="AA59" t="s">
-        <v>569</v>
+        <v>526</v>
       </c>
     </row>
     <row r="60" spans="1:27">
-      <c r="A60" s="2" t="s">
-        <v>570</v>
+      <c r="A60" s="5" t="s">
+        <v>527</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
@@ -10428,56 +10728,29 @@
         <v>0</v>
       </c>
       <c r="AA60" t="s">
-        <v>571</v>
+        <v>528</v>
       </c>
     </row>
     <row r="61" spans="1:27">
-      <c r="A61" s="2" t="s">
-        <v>572</v>
+      <c r="A61" s="5" t="s">
+        <v>529</v>
       </c>
       <c r="B61" t="s">
         <v>28</v>
       </c>
       <c r="C61" t="s">
-        <v>18</v>
-      </c>
-      <c r="D61" t="s">
-        <v>523</v>
-      </c>
-      <c r="K61" t="s">
-        <v>573</v>
-      </c>
-      <c r="L61" t="s">
-        <v>574</v>
-      </c>
-      <c r="M61" t="s">
-        <v>575</v>
-      </c>
-      <c r="N61" t="s">
-        <v>576</v>
-      </c>
-      <c r="O61" t="s">
-        <v>577</v>
-      </c>
-      <c r="P61" t="s">
-        <v>578</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>579</v>
-      </c>
-      <c r="R61" t="s">
-        <v>580</v>
+        <v>140</v>
       </c>
       <c r="Z61">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="s">
-        <v>581</v>
+        <v>530</v>
       </c>
     </row>
     <row r="62" spans="1:27">
-      <c r="A62" s="2" t="s">
-        <v>582</v>
+      <c r="A62" s="5" t="s">
+        <v>531</v>
       </c>
       <c r="B62" t="s">
         <v>106</v>
@@ -10489,12 +10762,12 @@
         <v>0</v>
       </c>
       <c r="AA62" t="s">
-        <v>583</v>
+        <v>532</v>
       </c>
     </row>
     <row r="63" spans="1:27">
-      <c r="A63" s="2" t="s">
-        <v>584</v>
+      <c r="A63" s="5" t="s">
+        <v>533</v>
       </c>
       <c r="B63" t="s">
         <v>346</v>
@@ -10506,12 +10779,12 @@
         <v>0</v>
       </c>
       <c r="AA63" t="s">
-        <v>585</v>
+        <v>534</v>
       </c>
     </row>
     <row r="64" spans="1:27">
-      <c r="A64" s="2" t="s">
-        <v>586</v>
+      <c r="A64" s="5" t="s">
+        <v>535</v>
       </c>
       <c r="B64" t="s">
         <v>346</v>
@@ -10520,30 +10793,24 @@
         <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>587</v>
-      </c>
-      <c r="M64" t="s">
-        <v>588</v>
-      </c>
-      <c r="N64" t="s">
-        <v>589</v>
-      </c>
-      <c r="O64" t="s">
-        <v>590</v>
+        <v>1273</v>
+      </c>
+      <c r="K64" t="s">
+        <v>1272</v>
       </c>
       <c r="P64" t="s">
-        <v>591</v>
+        <v>1271</v>
       </c>
       <c r="Z64">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA64" t="s">
-        <v>592</v>
+        <v>537</v>
       </c>
     </row>
     <row r="65" spans="1:27">
-      <c r="A65" s="2" t="s">
-        <v>593</v>
+      <c r="A65" s="5" t="s">
+        <v>538</v>
       </c>
       <c r="B65" t="s">
         <v>63</v>
@@ -10552,27 +10819,27 @@
         <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>594</v>
+        <v>539</v>
       </c>
       <c r="O65" t="s">
-        <v>595</v>
+        <v>540</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>1270</v>
       </c>
       <c r="S65" t="s">
-        <v>596</v>
-      </c>
-      <c r="W65" t="s">
-        <v>597</v>
+        <v>541</v>
       </c>
       <c r="Z65">
         <v>3</v>
       </c>
       <c r="AA65" t="s">
-        <v>598</v>
+        <v>542</v>
       </c>
     </row>
     <row r="66" spans="1:27">
-      <c r="A66" s="2" t="s">
-        <v>599</v>
+      <c r="A66" s="5" t="s">
+        <v>543</v>
       </c>
       <c r="B66" t="s">
         <v>58</v>
@@ -10584,12 +10851,12 @@
         <v>0</v>
       </c>
       <c r="AA66" t="s">
-        <v>600</v>
+        <v>544</v>
       </c>
     </row>
     <row r="67" spans="1:27">
-      <c r="A67" s="2" t="s">
-        <v>601</v>
+      <c r="A67" s="5" t="s">
+        <v>545</v>
       </c>
       <c r="B67" t="s">
         <v>188</v>
@@ -10601,12 +10868,12 @@
         <v>0</v>
       </c>
       <c r="AA67" t="s">
-        <v>602</v>
+        <v>546</v>
       </c>
     </row>
     <row r="68" spans="1:27">
-      <c r="A68" s="2" t="s">
-        <v>603</v>
+      <c r="A68" s="5" t="s">
+        <v>547</v>
       </c>
       <c r="B68" t="s">
         <v>10</v>
@@ -10618,12 +10885,12 @@
         <v>0</v>
       </c>
       <c r="AA68" t="s">
-        <v>604</v>
+        <v>548</v>
       </c>
     </row>
     <row r="69" spans="1:27">
-      <c r="A69" s="2" t="s">
-        <v>605</v>
+      <c r="A69" s="5" t="s">
+        <v>549</v>
       </c>
       <c r="B69" t="s">
         <v>10</v>
@@ -10635,12 +10902,12 @@
         <v>0</v>
       </c>
       <c r="AA69" t="s">
-        <v>606</v>
+        <v>550</v>
       </c>
     </row>
     <row r="70" spans="1:27">
-      <c r="A70" s="2" t="s">
-        <v>607</v>
+      <c r="A70" s="5" t="s">
+        <v>551</v>
       </c>
       <c r="B70" t="s">
         <v>106</v>
@@ -10652,29 +10919,35 @@
         <v>0</v>
       </c>
       <c r="AA70" t="s">
-        <v>608</v>
+        <v>552</v>
       </c>
     </row>
     <row r="71" spans="1:27">
-      <c r="A71" s="2" t="s">
-        <v>609</v>
+      <c r="A71" s="5" t="s">
+        <v>553</v>
       </c>
       <c r="B71" t="s">
         <v>188</v>
       </c>
       <c r="C71" t="s">
-        <v>140</v>
+        <v>18</v>
+      </c>
+      <c r="D71" t="s">
+        <v>1269</v>
+      </c>
+      <c r="T71" t="s">
+        <v>1268</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA71" t="s">
-        <v>610</v>
+        <v>554</v>
       </c>
     </row>
     <row r="72" spans="1:27">
-      <c r="A72" s="2" t="s">
-        <v>611</v>
+      <c r="A72" s="5" t="s">
+        <v>555</v>
       </c>
       <c r="B72" t="s">
         <v>17</v>
@@ -10686,12 +10959,12 @@
         <v>0</v>
       </c>
       <c r="AA72" t="s">
-        <v>612</v>
+        <v>556</v>
       </c>
     </row>
     <row r="73" spans="1:27">
-      <c r="A73" s="2" t="s">
-        <v>613</v>
+      <c r="A73" s="5" t="s">
+        <v>557</v>
       </c>
       <c r="B73" t="s">
         <v>106</v>
@@ -10699,19 +10972,22 @@
       <c r="C73" t="s">
         <v>18</v>
       </c>
+      <c r="D73" t="s">
+        <v>1267</v>
+      </c>
       <c r="U73" t="s">
-        <v>614</v>
+        <v>1266</v>
       </c>
       <c r="Z73">
         <v>1</v>
       </c>
       <c r="AA73" t="s">
-        <v>615</v>
+        <v>558</v>
       </c>
     </row>
     <row r="74" spans="1:27">
-      <c r="A74" s="2" t="s">
-        <v>616</v>
+      <c r="A74" s="5" t="s">
+        <v>559</v>
       </c>
       <c r="B74" t="s">
         <v>58</v>
@@ -10723,12 +10999,12 @@
         <v>0</v>
       </c>
       <c r="AA74" t="s">
-        <v>617</v>
+        <v>560</v>
       </c>
     </row>
     <row r="75" spans="1:27">
-      <c r="A75" s="2" t="s">
-        <v>618</v>
+      <c r="A75" s="5" t="s">
+        <v>561</v>
       </c>
       <c r="B75" t="s">
         <v>58</v>
@@ -10737,21 +11013,21 @@
         <v>18</v>
       </c>
       <c r="D75" t="s">
-        <v>619</v>
+        <v>562</v>
       </c>
       <c r="T75" t="s">
-        <v>620</v>
+        <v>563</v>
       </c>
       <c r="Z75">
         <v>1</v>
       </c>
       <c r="AA75" t="s">
-        <v>621</v>
+        <v>564</v>
       </c>
     </row>
     <row r="76" spans="1:27">
-      <c r="A76" s="2" t="s">
-        <v>622</v>
+      <c r="A76" s="5" t="s">
+        <v>565</v>
       </c>
       <c r="B76" t="s">
         <v>38</v>
@@ -10763,35 +11039,29 @@
         <v>0</v>
       </c>
       <c r="AA76" t="s">
-        <v>623</v>
+        <v>566</v>
       </c>
     </row>
     <row r="77" spans="1:27">
-      <c r="A77" s="2" t="s">
-        <v>624</v>
+      <c r="A77" s="5" t="s">
+        <v>567</v>
       </c>
       <c r="B77" t="s">
         <v>106</v>
       </c>
       <c r="C77" t="s">
-        <v>18</v>
-      </c>
-      <c r="D77" t="s">
-        <v>625</v>
-      </c>
-      <c r="X77" t="s">
-        <v>626</v>
+        <v>140</v>
       </c>
       <c r="Z77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="s">
-        <v>627</v>
+        <v>568</v>
       </c>
     </row>
     <row r="78" spans="1:27">
-      <c r="A78" s="2" t="s">
-        <v>628</v>
+      <c r="A78" s="5" t="s">
+        <v>569</v>
       </c>
       <c r="B78" t="s">
         <v>346</v>
@@ -10803,12 +11073,12 @@
         <v>0</v>
       </c>
       <c r="AA78" t="s">
-        <v>629</v>
+        <v>570</v>
       </c>
     </row>
     <row r="79" spans="1:27">
-      <c r="A79" s="2" t="s">
-        <v>630</v>
+      <c r="A79" s="5" t="s">
+        <v>571</v>
       </c>
       <c r="B79" t="s">
         <v>346</v>
@@ -10820,12 +11090,12 @@
         <v>0</v>
       </c>
       <c r="AA79" t="s">
-        <v>631</v>
+        <v>572</v>
       </c>
     </row>
     <row r="80" spans="1:27">
-      <c r="A80" s="2" t="s">
-        <v>632</v>
+      <c r="A80" s="5" t="s">
+        <v>573</v>
       </c>
       <c r="B80" t="s">
         <v>346</v>
@@ -10837,12 +11107,12 @@
         <v>0</v>
       </c>
       <c r="AA80" t="s">
-        <v>633</v>
+        <v>574</v>
       </c>
     </row>
     <row r="81" spans="1:27">
-      <c r="A81" s="2" t="s">
-        <v>634</v>
+      <c r="A81" s="5" t="s">
+        <v>575</v>
       </c>
       <c r="B81" t="s">
         <v>58</v>
@@ -10854,46 +11124,58 @@
         <v>0</v>
       </c>
       <c r="AA81" t="s">
-        <v>635</v>
+        <v>576</v>
       </c>
     </row>
     <row r="82" spans="1:27">
-      <c r="A82" s="2" t="s">
-        <v>636</v>
+      <c r="A82" s="5" t="s">
+        <v>577</v>
       </c>
       <c r="B82" t="s">
         <v>63</v>
       </c>
       <c r="C82" t="s">
-        <v>140</v>
+        <v>18</v>
+      </c>
+      <c r="D82" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I82" t="s">
+        <v>1264</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA82" t="s">
-        <v>637</v>
+        <v>578</v>
       </c>
     </row>
     <row r="83" spans="1:27">
-      <c r="A83" s="2" t="s">
-        <v>638</v>
+      <c r="A83" s="5" t="s">
+        <v>579</v>
       </c>
       <c r="B83" t="s">
         <v>63</v>
       </c>
       <c r="C83" t="s">
-        <v>140</v>
+        <v>18</v>
+      </c>
+      <c r="D83" t="s">
+        <v>1263</v>
+      </c>
+      <c r="T83" t="s">
+        <v>1262</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA83" t="s">
-        <v>639</v>
+        <v>580</v>
       </c>
     </row>
     <row r="84" spans="1:27">
-      <c r="A84" s="2" t="s">
-        <v>640</v>
+      <c r="A84" s="5" t="s">
+        <v>581</v>
       </c>
       <c r="B84" t="s">
         <v>14</v>
@@ -10905,12 +11187,12 @@
         <v>0</v>
       </c>
       <c r="AA84" t="s">
-        <v>641</v>
+        <v>582</v>
       </c>
     </row>
     <row r="85" spans="1:27">
-      <c r="A85" s="2" t="s">
-        <v>642</v>
+      <c r="A85" s="5" t="s">
+        <v>583</v>
       </c>
       <c r="B85" t="s">
         <v>17</v>
@@ -10922,12 +11204,12 @@
         <v>0</v>
       </c>
       <c r="AA85" t="s">
-        <v>643</v>
+        <v>584</v>
       </c>
     </row>
     <row r="86" spans="1:27">
-      <c r="A86" s="2" t="s">
-        <v>644</v>
+      <c r="A86" s="5" t="s">
+        <v>585</v>
       </c>
       <c r="B86" t="s">
         <v>14</v>
@@ -10939,12 +11221,12 @@
         <v>0</v>
       </c>
       <c r="AA86" t="s">
-        <v>645</v>
+        <v>586</v>
       </c>
     </row>
     <row r="87" spans="1:27">
-      <c r="A87" s="2" t="s">
-        <v>646</v>
+      <c r="A87" s="5" t="s">
+        <v>587</v>
       </c>
       <c r="B87" t="s">
         <v>106</v>
@@ -10956,12 +11238,12 @@
         <v>0</v>
       </c>
       <c r="AA87" t="s">
-        <v>647</v>
+        <v>588</v>
       </c>
     </row>
     <row r="88" spans="1:27">
-      <c r="A88" s="2" t="s">
-        <v>648</v>
+      <c r="A88" s="5" t="s">
+        <v>589</v>
       </c>
       <c r="B88" t="s">
         <v>346</v>
@@ -10970,24 +11252,24 @@
         <v>18</v>
       </c>
       <c r="D88" t="s">
-        <v>649</v>
+        <v>590</v>
       </c>
       <c r="N88" t="s">
-        <v>650</v>
+        <v>591</v>
       </c>
       <c r="Z88">
         <v>1</v>
       </c>
       <c r="AA88" t="s">
-        <v>651</v>
+        <v>592</v>
       </c>
     </row>
     <row r="89" spans="1:27">
-      <c r="A89" s="2" t="s">
-        <v>652</v>
+      <c r="A89" s="5" t="s">
+        <v>593</v>
       </c>
       <c r="B89" t="s">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="C89" t="s">
         <v>140</v>
@@ -10996,12 +11278,12 @@
         <v>0</v>
       </c>
       <c r="AA89" t="s">
-        <v>653</v>
+        <v>594</v>
       </c>
     </row>
     <row r="90" spans="1:27">
-      <c r="A90" s="2" t="s">
-        <v>654</v>
+      <c r="A90" s="5" t="s">
+        <v>595</v>
       </c>
       <c r="B90" t="s">
         <v>106</v>
@@ -11013,12 +11295,12 @@
         <v>0</v>
       </c>
       <c r="AA90" t="s">
-        <v>655</v>
+        <v>596</v>
       </c>
     </row>
     <row r="91" spans="1:27">
-      <c r="A91" s="2" t="s">
-        <v>656</v>
+      <c r="A91" s="5" t="s">
+        <v>597</v>
       </c>
       <c r="B91" t="s">
         <v>17</v>
@@ -11030,12 +11312,12 @@
         <v>0</v>
       </c>
       <c r="AA91" t="s">
-        <v>657</v>
+        <v>598</v>
       </c>
     </row>
     <row r="92" spans="1:27">
-      <c r="A92" s="2" t="s">
-        <v>658</v>
+      <c r="A92" s="5" t="s">
+        <v>599</v>
       </c>
       <c r="B92" t="s">
         <v>79</v>
@@ -11047,12 +11329,12 @@
         <v>0</v>
       </c>
       <c r="AA92" t="s">
-        <v>659</v>
+        <v>600</v>
       </c>
     </row>
     <row r="93" spans="1:27">
-      <c r="A93" s="2" t="s">
-        <v>660</v>
+      <c r="A93" s="5" t="s">
+        <v>601</v>
       </c>
       <c r="B93" t="s">
         <v>152</v>
@@ -11064,12 +11346,12 @@
         <v>0</v>
       </c>
       <c r="AA93" t="s">
-        <v>661</v>
+        <v>602</v>
       </c>
     </row>
     <row r="94" spans="1:27">
-      <c r="A94" s="2" t="s">
-        <v>662</v>
+      <c r="A94" s="5" t="s">
+        <v>603</v>
       </c>
       <c r="B94" t="s">
         <v>63</v>
@@ -11081,12 +11363,12 @@
         <v>0</v>
       </c>
       <c r="AA94" t="s">
-        <v>663</v>
+        <v>604</v>
       </c>
     </row>
     <row r="95" spans="1:27">
-      <c r="A95" s="2" t="s">
-        <v>664</v>
+      <c r="A95" s="5" t="s">
+        <v>605</v>
       </c>
       <c r="B95" t="s">
         <v>17</v>
@@ -11098,29 +11380,35 @@
         <v>0</v>
       </c>
       <c r="AA95" t="s">
-        <v>665</v>
+        <v>606</v>
       </c>
     </row>
     <row r="96" spans="1:27">
-      <c r="A96" s="2" t="s">
-        <v>666</v>
+      <c r="A96" s="5" t="s">
+        <v>607</v>
       </c>
       <c r="B96" t="s">
         <v>188</v>
       </c>
       <c r="C96" t="s">
-        <v>140</v>
+        <v>18</v>
+      </c>
+      <c r="D96" t="s">
+        <v>1261</v>
+      </c>
+      <c r="O96" t="s">
+        <v>1260</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA96" t="s">
-        <v>667</v>
+        <v>608</v>
       </c>
     </row>
     <row r="97" spans="1:27">
-      <c r="A97" s="2" t="s">
-        <v>668</v>
+      <c r="A97" s="5" t="s">
+        <v>609</v>
       </c>
       <c r="B97" t="s">
         <v>346</v>
@@ -11129,33 +11417,24 @@
         <v>18</v>
       </c>
       <c r="D97" t="s">
-        <v>669</v>
+        <v>488</v>
       </c>
       <c r="M97" t="s">
-        <v>670</v>
-      </c>
-      <c r="N97" t="s">
-        <v>671</v>
-      </c>
-      <c r="O97" t="s">
-        <v>672</v>
+        <v>1259</v>
       </c>
       <c r="Q97" t="s">
-        <v>673</v>
-      </c>
-      <c r="R97" t="s">
-        <v>674</v>
+        <v>1258</v>
       </c>
       <c r="Z97">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA97" t="s">
-        <v>675</v>
+        <v>611</v>
       </c>
     </row>
     <row r="98" spans="1:27">
-      <c r="A98" s="2" t="s">
-        <v>676</v>
+      <c r="A98" s="5" t="s">
+        <v>612</v>
       </c>
       <c r="B98" t="s">
         <v>63</v>
@@ -11164,21 +11443,24 @@
         <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>677</v>
+        <v>1257</v>
+      </c>
+      <c r="I98" t="s">
+        <v>1256</v>
       </c>
       <c r="K98" t="s">
-        <v>678</v>
+        <v>613</v>
       </c>
       <c r="Z98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA98" t="s">
-        <v>679</v>
+        <v>614</v>
       </c>
     </row>
     <row r="99" spans="1:27">
-      <c r="A99" s="2" t="s">
-        <v>680</v>
+      <c r="A99" s="5" t="s">
+        <v>615</v>
       </c>
       <c r="B99" t="s">
         <v>346</v>
@@ -11190,12 +11472,12 @@
         <v>0</v>
       </c>
       <c r="AA99" t="s">
-        <v>681</v>
+        <v>616</v>
       </c>
     </row>
     <row r="100" spans="1:27">
-      <c r="A100" s="2" t="s">
-        <v>682</v>
+      <c r="A100" s="5" t="s">
+        <v>617</v>
       </c>
       <c r="B100" t="s">
         <v>38</v>
@@ -11204,39 +11486,24 @@
         <v>18</v>
       </c>
       <c r="D100" t="s">
-        <v>683</v>
-      </c>
-      <c r="K100" t="s">
-        <v>684</v>
+        <v>1255</v>
       </c>
       <c r="L100" t="s">
-        <v>685</v>
-      </c>
-      <c r="M100" t="s">
-        <v>686</v>
-      </c>
-      <c r="N100" t="s">
-        <v>687</v>
-      </c>
-      <c r="O100" t="s">
-        <v>688</v>
-      </c>
-      <c r="P100" t="s">
-        <v>689</v>
+        <v>619</v>
       </c>
       <c r="Z100">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA100" t="s">
-        <v>690</v>
+        <v>620</v>
       </c>
     </row>
     <row r="101" spans="1:27">
-      <c r="A101" s="2" t="s">
-        <v>691</v>
+      <c r="A101" s="5" t="s">
+        <v>621</v>
       </c>
       <c r="B101" t="s">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="C101" t="s">
         <v>140</v>
@@ -11245,12 +11512,12 @@
         <v>0</v>
       </c>
       <c r="AA101" t="s">
-        <v>692</v>
+        <v>622</v>
       </c>
     </row>
     <row r="102" spans="1:27">
-      <c r="A102" s="2" t="s">
-        <v>693</v>
+      <c r="A102" s="5" t="s">
+        <v>623</v>
       </c>
       <c r="B102" t="s">
         <v>38</v>
@@ -11262,12 +11529,12 @@
         <v>0</v>
       </c>
       <c r="AA102" t="s">
-        <v>694</v>
+        <v>624</v>
       </c>
     </row>
     <row r="103" spans="1:27">
-      <c r="A103" s="2" t="s">
-        <v>695</v>
+      <c r="A103" s="5" t="s">
+        <v>625</v>
       </c>
       <c r="B103" t="s">
         <v>346</v>
@@ -11279,15 +11546,15 @@
         <v>0</v>
       </c>
       <c r="AA103" t="s">
-        <v>696</v>
+        <v>626</v>
       </c>
     </row>
     <row r="104" spans="1:27">
-      <c r="A104" s="2" t="s">
-        <v>697</v>
+      <c r="A104" s="5" t="s">
+        <v>627</v>
       </c>
       <c r="B104" t="s">
-        <v>698</v>
+        <v>628</v>
       </c>
       <c r="C104" t="s">
         <v>140</v>
@@ -11296,35 +11563,29 @@
         <v>0</v>
       </c>
       <c r="AA104" t="s">
-        <v>699</v>
+        <v>629</v>
       </c>
     </row>
     <row r="105" spans="1:27">
-      <c r="A105" s="2" t="s">
-        <v>700</v>
+      <c r="A105" s="5" t="s">
+        <v>630</v>
       </c>
       <c r="B105" t="s">
         <v>106</v>
       </c>
       <c r="C105" t="s">
-        <v>18</v>
-      </c>
-      <c r="D105" t="s">
-        <v>677</v>
-      </c>
-      <c r="K105" t="s">
-        <v>701</v>
+        <v>140</v>
       </c>
       <c r="Z105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="s">
-        <v>702</v>
+        <v>631</v>
       </c>
     </row>
     <row r="106" spans="1:27">
-      <c r="A106" s="2" t="s">
-        <v>703</v>
+      <c r="A106" s="5" t="s">
+        <v>632</v>
       </c>
       <c r="B106" t="s">
         <v>14</v>
@@ -11333,24 +11594,21 @@
         <v>18</v>
       </c>
       <c r="D106" t="s">
-        <v>704</v>
+        <v>633</v>
       </c>
       <c r="N106" t="s">
-        <v>705</v>
-      </c>
-      <c r="O106" t="s">
-        <v>706</v>
+        <v>634</v>
       </c>
       <c r="Z106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA106" t="s">
-        <v>707</v>
+        <v>635</v>
       </c>
     </row>
     <row r="107" spans="1:27">
-      <c r="A107" s="2" t="s">
-        <v>708</v>
+      <c r="A107" s="5" t="s">
+        <v>636</v>
       </c>
       <c r="B107" t="s">
         <v>155</v>
@@ -11362,12 +11620,12 @@
         <v>0</v>
       </c>
       <c r="AA107" t="s">
-        <v>709</v>
+        <v>637</v>
       </c>
     </row>
     <row r="108" spans="1:27">
-      <c r="A108" s="2" t="s">
-        <v>710</v>
+      <c r="A108" s="5" t="s">
+        <v>638</v>
       </c>
       <c r="B108" t="s">
         <v>38</v>
@@ -11376,30 +11634,27 @@
         <v>18</v>
       </c>
       <c r="D108" t="s">
-        <v>711</v>
-      </c>
-      <c r="H108" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="N108" t="s">
-        <v>713</v>
+        <v>639</v>
       </c>
       <c r="O108" t="s">
-        <v>714</v>
+        <v>640</v>
       </c>
       <c r="Q108" t="s">
-        <v>715</v>
+        <v>641</v>
       </c>
       <c r="Z108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA108" t="s">
-        <v>716</v>
+        <v>642</v>
       </c>
     </row>
     <row r="109" spans="1:27">
-      <c r="A109" s="2" t="s">
-        <v>717</v>
+      <c r="A109" s="5" t="s">
+        <v>643</v>
       </c>
       <c r="B109" t="s">
         <v>152</v>
@@ -11411,12 +11666,12 @@
         <v>0</v>
       </c>
       <c r="AA109" t="s">
-        <v>718</v>
+        <v>644</v>
       </c>
     </row>
     <row r="110" spans="1:27">
-      <c r="A110" s="2" t="s">
-        <v>719</v>
+      <c r="A110" s="5" t="s">
+        <v>645</v>
       </c>
       <c r="B110" t="s">
         <v>28</v>
@@ -11425,24 +11680,27 @@
         <v>18</v>
       </c>
       <c r="D110" t="s">
-        <v>669</v>
+        <v>610</v>
       </c>
       <c r="M110" t="s">
-        <v>720</v>
+        <v>646</v>
       </c>
       <c r="N110" t="s">
-        <v>721</v>
+        <v>1254</v>
+      </c>
+      <c r="P110" t="s">
+        <v>1253</v>
       </c>
       <c r="Z110">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA110" t="s">
-        <v>722</v>
+        <v>647</v>
       </c>
     </row>
     <row r="111" spans="1:27">
-      <c r="A111" s="2" t="s">
-        <v>723</v>
+      <c r="A111" s="5" t="s">
+        <v>648</v>
       </c>
       <c r="B111" t="s">
         <v>17</v>
@@ -11454,12 +11712,12 @@
         <v>0</v>
       </c>
       <c r="AA111" t="s">
-        <v>724</v>
+        <v>649</v>
       </c>
     </row>
     <row r="112" spans="1:27">
-      <c r="A112" s="2" t="s">
-        <v>725</v>
+      <c r="A112" s="5" t="s">
+        <v>650</v>
       </c>
       <c r="B112" t="s">
         <v>38</v>
@@ -11468,21 +11726,21 @@
         <v>18</v>
       </c>
       <c r="D112" t="s">
-        <v>726</v>
+        <v>651</v>
       </c>
       <c r="L112" t="s">
-        <v>727</v>
+        <v>652</v>
       </c>
       <c r="Z112">
         <v>1</v>
       </c>
       <c r="AA112" t="s">
-        <v>728</v>
+        <v>653</v>
       </c>
     </row>
     <row r="113" spans="1:27">
-      <c r="A113" s="2" t="s">
-        <v>729</v>
+      <c r="A113" s="5" t="s">
+        <v>654</v>
       </c>
       <c r="B113" t="s">
         <v>38</v>
@@ -11491,73 +11749,67 @@
         <v>18</v>
       </c>
       <c r="D113" t="s">
-        <v>730</v>
+        <v>655</v>
       </c>
       <c r="I113" t="s">
-        <v>731</v>
+        <v>656</v>
       </c>
       <c r="P113" t="s">
-        <v>732</v>
+        <v>657</v>
       </c>
       <c r="S113" t="s">
-        <v>733</v>
+        <v>658</v>
       </c>
       <c r="Z113">
         <v>3</v>
       </c>
       <c r="AA113" t="s">
-        <v>734</v>
+        <v>659</v>
       </c>
     </row>
     <row r="114" spans="1:27">
-      <c r="A114" s="2" t="s">
-        <v>735</v>
+      <c r="A114" s="5" t="s">
+        <v>660</v>
       </c>
       <c r="B114" t="s">
         <v>63</v>
       </c>
       <c r="C114" t="s">
-        <v>140</v>
+        <v>18</v>
+      </c>
+      <c r="D114" t="s">
+        <v>1252</v>
+      </c>
+      <c r="M114" t="s">
+        <v>1251</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA114" t="s">
-        <v>736</v>
+        <v>661</v>
       </c>
     </row>
     <row r="115" spans="1:27">
-      <c r="A115" s="2" t="s">
-        <v>737</v>
+      <c r="A115" s="5" t="s">
+        <v>662</v>
       </c>
       <c r="B115" t="s">
         <v>10</v>
       </c>
       <c r="C115" t="s">
-        <v>18</v>
-      </c>
-      <c r="D115" t="s">
-        <v>669</v>
-      </c>
-      <c r="M115" t="s">
-        <v>738</v>
-      </c>
-      <c r="N115" t="s">
-        <v>739</v>
-      </c>
-      <c r="O115" t="s">
-        <v>740</v>
+        <v>140</v>
       </c>
       <c r="Z115">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="s">
-        <v>741</v>
+        <v>663</v>
       </c>
     </row>
     <row r="116" spans="1:27">
-      <c r="A116" s="2" t="s">
-        <v>742</v>
+      <c r="A116" s="5" t="s">
+        <v>664</v>
       </c>
       <c r="B116" t="s">
         <v>106</v>
@@ -11566,21 +11818,21 @@
         <v>18</v>
       </c>
       <c r="D116" t="s">
-        <v>562</v>
+        <v>520</v>
       </c>
       <c r="L116" t="s">
-        <v>743</v>
+        <v>665</v>
       </c>
       <c r="Z116">
         <v>1</v>
       </c>
       <c r="AA116" t="s">
-        <v>744</v>
+        <v>666</v>
       </c>
     </row>
     <row r="117" spans="1:27">
-      <c r="A117" s="2" t="s">
-        <v>745</v>
+      <c r="A117" s="5" t="s">
+        <v>667</v>
       </c>
       <c r="B117" t="s">
         <v>63</v>
@@ -11592,12 +11844,12 @@
         <v>0</v>
       </c>
       <c r="AA117" t="s">
-        <v>746</v>
+        <v>668</v>
       </c>
     </row>
     <row r="118" spans="1:27">
-      <c r="A118" s="2" t="s">
-        <v>747</v>
+      <c r="A118" s="5" t="s">
+        <v>669</v>
       </c>
       <c r="B118" t="s">
         <v>152</v>
@@ -11609,12 +11861,12 @@
         <v>0</v>
       </c>
       <c r="AA118" t="s">
-        <v>748</v>
+        <v>670</v>
       </c>
     </row>
     <row r="119" spans="1:27">
-      <c r="A119" s="2" t="s">
-        <v>749</v>
+      <c r="A119" s="5" t="s">
+        <v>671</v>
       </c>
       <c r="B119" t="s">
         <v>346</v>
@@ -11623,27 +11875,30 @@
         <v>18</v>
       </c>
       <c r="D119" t="s">
-        <v>750</v>
+        <v>618</v>
+      </c>
+      <c r="K119" t="s">
+        <v>1250</v>
       </c>
       <c r="L119" t="s">
-        <v>751</v>
-      </c>
-      <c r="O119" t="s">
-        <v>752</v>
+        <v>673</v>
       </c>
       <c r="Q119" t="s">
-        <v>753</v>
+        <v>674</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>1249</v>
       </c>
       <c r="Z119">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA119" t="s">
-        <v>754</v>
+        <v>675</v>
       </c>
     </row>
     <row r="120" spans="1:27">
-      <c r="A120" s="2" t="s">
-        <v>755</v>
+      <c r="A120" s="5" t="s">
+        <v>676</v>
       </c>
       <c r="B120" t="s">
         <v>63</v>
@@ -11652,45 +11907,33 @@
         <v>18</v>
       </c>
       <c r="D120" t="s">
-        <v>756</v>
+        <v>482</v>
       </c>
       <c r="J120" t="s">
-        <v>757</v>
+        <v>1248</v>
       </c>
       <c r="L120" t="s">
-        <v>758</v>
-      </c>
-      <c r="M120" t="s">
-        <v>759</v>
+        <v>677</v>
       </c>
       <c r="N120" t="s">
-        <v>760</v>
-      </c>
-      <c r="O120" t="s">
-        <v>761</v>
-      </c>
-      <c r="P120" t="s">
-        <v>762</v>
-      </c>
-      <c r="Q120" t="s">
-        <v>763</v>
-      </c>
-      <c r="T120" t="s">
-        <v>764</v>
+        <v>1247</v>
+      </c>
+      <c r="S120" t="s">
+        <v>1246</v>
       </c>
       <c r="Z120">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AA120" t="s">
-        <v>765</v>
+        <v>678</v>
       </c>
     </row>
     <row r="121" spans="1:27">
-      <c r="A121" s="2" t="s">
-        <v>766</v>
+      <c r="A121" s="5" t="s">
+        <v>679</v>
       </c>
       <c r="B121" t="s">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="C121" t="s">
         <v>140</v>
@@ -11699,12 +11942,12 @@
         <v>0</v>
       </c>
       <c r="AA121" t="s">
-        <v>767</v>
+        <v>680</v>
       </c>
     </row>
     <row r="122" spans="1:27">
-      <c r="A122" s="2" t="s">
-        <v>768</v>
+      <c r="A122" s="5" t="s">
+        <v>681</v>
       </c>
       <c r="B122" t="s">
         <v>58</v>
@@ -11716,12 +11959,12 @@
         <v>0</v>
       </c>
       <c r="AA122" t="s">
-        <v>769</v>
+        <v>682</v>
       </c>
     </row>
     <row r="123" spans="1:27">
-      <c r="A123" s="2" t="s">
-        <v>770</v>
+      <c r="A123" s="5" t="s">
+        <v>683</v>
       </c>
       <c r="B123" t="s">
         <v>28</v>
@@ -11730,30 +11973,24 @@
         <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>750</v>
+        <v>672</v>
       </c>
       <c r="L123" t="s">
-        <v>771</v>
+        <v>684</v>
       </c>
       <c r="N123" t="s">
-        <v>772</v>
-      </c>
-      <c r="P123" t="s">
-        <v>773</v>
-      </c>
-      <c r="S123" t="s">
-        <v>774</v>
+        <v>685</v>
       </c>
       <c r="Z123">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA123" t="s">
-        <v>775</v>
+        <v>686</v>
       </c>
     </row>
     <row r="124" spans="1:27">
-      <c r="A124" s="2" t="s">
-        <v>776</v>
+      <c r="A124" s="5" t="s">
+        <v>687</v>
       </c>
       <c r="B124" t="s">
         <v>155</v>
@@ -11765,12 +12002,12 @@
         <v>0</v>
       </c>
       <c r="AA124" t="s">
-        <v>777</v>
+        <v>688</v>
       </c>
     </row>
     <row r="125" spans="1:27">
-      <c r="A125" s="2" t="s">
-        <v>778</v>
+      <c r="A125" s="5" t="s">
+        <v>689</v>
       </c>
       <c r="B125" t="s">
         <v>58</v>
@@ -11782,12 +12019,12 @@
         <v>0</v>
       </c>
       <c r="AA125" t="s">
-        <v>779</v>
+        <v>690</v>
       </c>
     </row>
     <row r="126" spans="1:27">
-      <c r="A126" s="2" t="s">
-        <v>780</v>
+      <c r="A126" s="5" t="s">
+        <v>691</v>
       </c>
       <c r="B126" t="s">
         <v>17</v>
@@ -11799,29 +12036,35 @@
         <v>0</v>
       </c>
       <c r="AA126" t="s">
-        <v>781</v>
+        <v>692</v>
       </c>
     </row>
     <row r="127" spans="1:27">
-      <c r="A127" s="2" t="s">
-        <v>782</v>
+      <c r="A127" s="5" t="s">
+        <v>693</v>
       </c>
       <c r="B127" t="s">
         <v>28</v>
       </c>
       <c r="C127" t="s">
-        <v>140</v>
+        <v>18</v>
+      </c>
+      <c r="D127" t="s">
+        <v>1245</v>
+      </c>
+      <c r="W127" t="s">
+        <v>1244</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA127" t="s">
-        <v>783</v>
+        <v>694</v>
       </c>
     </row>
     <row r="128" spans="1:27">
-      <c r="A128" s="2" t="s">
-        <v>784</v>
+      <c r="A128" s="5" t="s">
+        <v>695</v>
       </c>
       <c r="B128" t="s">
         <v>17</v>
@@ -11833,12 +12076,12 @@
         <v>0</v>
       </c>
       <c r="AA128" t="s">
-        <v>785</v>
+        <v>696</v>
       </c>
     </row>
     <row r="129" spans="1:27">
-      <c r="A129" s="2" t="s">
-        <v>786</v>
+      <c r="A129" s="5" t="s">
+        <v>697</v>
       </c>
       <c r="B129" t="s">
         <v>79</v>
@@ -11850,12 +12093,12 @@
         <v>0</v>
       </c>
       <c r="AA129" t="s">
-        <v>787</v>
+        <v>698</v>
       </c>
     </row>
     <row r="130" spans="1:27">
-      <c r="A130" s="2" t="s">
-        <v>788</v>
+      <c r="A130" s="5" t="s">
+        <v>699</v>
       </c>
       <c r="B130" t="s">
         <v>58</v>
@@ -11864,21 +12107,21 @@
         <v>18</v>
       </c>
       <c r="D130" t="s">
-        <v>587</v>
-      </c>
-      <c r="M130" t="s">
-        <v>789</v>
+        <v>1243</v>
+      </c>
+      <c r="X130" t="s">
+        <v>1242</v>
       </c>
       <c r="Z130">
         <v>1</v>
       </c>
       <c r="AA130" t="s">
-        <v>790</v>
+        <v>700</v>
       </c>
     </row>
     <row r="131" spans="1:27">
-      <c r="A131" s="2" t="s">
-        <v>791</v>
+      <c r="A131" s="5" t="s">
+        <v>701</v>
       </c>
       <c r="B131" t="s">
         <v>17</v>
@@ -11890,12 +12133,12 @@
         <v>0</v>
       </c>
       <c r="AA131" t="s">
-        <v>792</v>
+        <v>702</v>
       </c>
     </row>
     <row r="132" spans="1:27">
-      <c r="A132" s="2" t="s">
-        <v>793</v>
+      <c r="A132" s="5" t="s">
+        <v>703</v>
       </c>
       <c r="B132" t="s">
         <v>172</v>
@@ -11907,12 +12150,12 @@
         <v>0</v>
       </c>
       <c r="AA132" t="s">
-        <v>794</v>
+        <v>704</v>
       </c>
     </row>
     <row r="133" spans="1:27">
-      <c r="A133" s="2" t="s">
-        <v>795</v>
+      <c r="A133" s="5" t="s">
+        <v>705</v>
       </c>
       <c r="B133" t="s">
         <v>188</v>
@@ -11924,12 +12167,12 @@
         <v>0</v>
       </c>
       <c r="AA133" t="s">
-        <v>796</v>
+        <v>706</v>
       </c>
     </row>
     <row r="134" spans="1:27">
-      <c r="A134" s="2" t="s">
-        <v>797</v>
+      <c r="A134" s="5" t="s">
+        <v>707</v>
       </c>
       <c r="B134" t="s">
         <v>346</v>
@@ -11941,12 +12184,12 @@
         <v>0</v>
       </c>
       <c r="AA134" t="s">
-        <v>798</v>
+        <v>708</v>
       </c>
     </row>
     <row r="135" spans="1:27">
-      <c r="A135" s="2" t="s">
-        <v>799</v>
+      <c r="A135" s="5" t="s">
+        <v>709</v>
       </c>
       <c r="B135" t="s">
         <v>17</v>
@@ -11958,12 +12201,12 @@
         <v>0</v>
       </c>
       <c r="AA135" t="s">
-        <v>800</v>
+        <v>710</v>
       </c>
     </row>
     <row r="136" spans="1:27">
-      <c r="A136" s="2" t="s">
-        <v>801</v>
+      <c r="A136" s="5" t="s">
+        <v>711</v>
       </c>
       <c r="B136" t="s">
         <v>106</v>
@@ -11975,12 +12218,12 @@
         <v>0</v>
       </c>
       <c r="AA136" t="s">
-        <v>802</v>
+        <v>712</v>
       </c>
     </row>
     <row r="137" spans="1:27">
-      <c r="A137" s="2" t="s">
-        <v>803</v>
+      <c r="A137" s="5" t="s">
+        <v>713</v>
       </c>
       <c r="B137" t="s">
         <v>14</v>
@@ -11989,38 +12232,44 @@
         <v>18</v>
       </c>
       <c r="D137" t="s">
-        <v>804</v>
-      </c>
-      <c r="N137" t="s">
-        <v>805</v>
+        <v>1241</v>
+      </c>
+      <c r="P137" t="s">
+        <v>1240</v>
       </c>
       <c r="Z137">
         <v>1</v>
       </c>
       <c r="AA137" t="s">
-        <v>806</v>
+        <v>715</v>
       </c>
     </row>
     <row r="138" spans="1:27">
-      <c r="A138" s="2" t="s">
-        <v>807</v>
+      <c r="A138" s="5" t="s">
+        <v>716</v>
       </c>
       <c r="B138" t="s">
         <v>106</v>
       </c>
       <c r="C138" t="s">
-        <v>140</v>
+        <v>18</v>
+      </c>
+      <c r="D138" t="s">
+        <v>1239</v>
+      </c>
+      <c r="Y138" t="s">
+        <v>1238</v>
       </c>
       <c r="Z138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA138" t="s">
-        <v>808</v>
+        <v>717</v>
       </c>
     </row>
     <row r="139" spans="1:27">
-      <c r="A139" s="2" t="s">
-        <v>809</v>
+      <c r="A139" s="5" t="s">
+        <v>718</v>
       </c>
       <c r="B139" t="s">
         <v>155</v>
@@ -12032,12 +12281,12 @@
         <v>0</v>
       </c>
       <c r="AA139" t="s">
-        <v>810</v>
+        <v>719</v>
       </c>
     </row>
     <row r="140" spans="1:27">
-      <c r="A140" s="2" t="s">
-        <v>811</v>
+      <c r="A140" s="5" t="s">
+        <v>720</v>
       </c>
       <c r="B140" t="s">
         <v>114</v>
@@ -12049,12 +12298,12 @@
         <v>0</v>
       </c>
       <c r="AA140" t="s">
-        <v>812</v>
+        <v>721</v>
       </c>
     </row>
     <row r="141" spans="1:27">
-      <c r="A141" s="2" t="s">
-        <v>813</v>
+      <c r="A141" s="5" t="s">
+        <v>722</v>
       </c>
       <c r="B141" t="s">
         <v>181</v>
@@ -12066,12 +12315,12 @@
         <v>0</v>
       </c>
       <c r="AA141" t="s">
-        <v>814</v>
+        <v>723</v>
       </c>
     </row>
     <row r="142" spans="1:27">
-      <c r="A142" s="2" t="s">
-        <v>815</v>
+      <c r="A142" s="5" t="s">
+        <v>724</v>
       </c>
       <c r="B142" t="s">
         <v>28</v>
@@ -12083,18 +12332,18 @@
         <v>19</v>
       </c>
       <c r="E142" t="s">
-        <v>816</v>
+        <v>725</v>
       </c>
       <c r="Z142">
         <v>1</v>
       </c>
       <c r="AA142" t="s">
-        <v>817</v>
+        <v>726</v>
       </c>
     </row>
     <row r="143" spans="1:27">
-      <c r="A143" s="2" t="s">
-        <v>818</v>
+      <c r="A143" s="5" t="s">
+        <v>727</v>
       </c>
       <c r="B143" t="s">
         <v>38</v>
@@ -12106,12 +12355,12 @@
         <v>0</v>
       </c>
       <c r="AA143" t="s">
-        <v>819</v>
+        <v>728</v>
       </c>
     </row>
     <row r="144" spans="1:27">
-      <c r="A144" s="2" t="s">
-        <v>820</v>
+      <c r="A144" s="5" t="s">
+        <v>729</v>
       </c>
       <c r="B144" t="s">
         <v>17</v>
@@ -12123,12 +12372,12 @@
         <v>0</v>
       </c>
       <c r="AA144" t="s">
-        <v>821</v>
+        <v>730</v>
       </c>
     </row>
     <row r="145" spans="1:27">
-      <c r="A145" s="2" t="s">
-        <v>822</v>
+      <c r="A145" s="5" t="s">
+        <v>731</v>
       </c>
       <c r="B145" t="s">
         <v>17</v>
@@ -12140,12 +12389,12 @@
         <v>0</v>
       </c>
       <c r="AA145" t="s">
-        <v>823</v>
+        <v>732</v>
       </c>
     </row>
     <row r="146" spans="1:27">
-      <c r="A146" s="2" t="s">
-        <v>824</v>
+      <c r="A146" s="5" t="s">
+        <v>733</v>
       </c>
       <c r="B146" t="s">
         <v>346</v>
@@ -12154,27 +12403,24 @@
         <v>18</v>
       </c>
       <c r="D146" t="s">
-        <v>825</v>
-      </c>
-      <c r="K146" t="s">
-        <v>826</v>
+        <v>488</v>
       </c>
       <c r="M146" t="s">
-        <v>827</v>
+        <v>734</v>
       </c>
       <c r="Z146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA146" t="s">
-        <v>828</v>
+        <v>735</v>
       </c>
     </row>
     <row r="147" spans="1:27">
-      <c r="A147" s="2" t="s">
-        <v>829</v>
+      <c r="A147" s="5" t="s">
+        <v>736</v>
       </c>
       <c r="B147" t="s">
-        <v>698</v>
+        <v>628</v>
       </c>
       <c r="C147" t="s">
         <v>140</v>
@@ -12183,12 +12429,12 @@
         <v>0</v>
       </c>
       <c r="AA147" t="s">
-        <v>830</v>
+        <v>737</v>
       </c>
     </row>
     <row r="148" spans="1:27">
-      <c r="A148" s="2" t="s">
-        <v>831</v>
+      <c r="A148" s="5" t="s">
+        <v>738</v>
       </c>
       <c r="B148" t="s">
         <v>346</v>
@@ -12200,12 +12446,12 @@
         <v>0</v>
       </c>
       <c r="AA148" t="s">
-        <v>832</v>
+        <v>739</v>
       </c>
     </row>
     <row r="149" spans="1:27">
-      <c r="A149" s="2" t="s">
-        <v>833</v>
+      <c r="A149" s="5" t="s">
+        <v>740</v>
       </c>
       <c r="B149" t="s">
         <v>14</v>
@@ -12217,12 +12463,12 @@
         <v>0</v>
       </c>
       <c r="AA149" t="s">
-        <v>834</v>
+        <v>741</v>
       </c>
     </row>
     <row r="150" spans="1:27">
-      <c r="A150" s="2" t="s">
-        <v>835</v>
+      <c r="A150" s="5" t="s">
+        <v>742</v>
       </c>
       <c r="B150" t="s">
         <v>106</v>
@@ -12234,12 +12480,12 @@
         <v>0</v>
       </c>
       <c r="AA150" t="s">
-        <v>836</v>
+        <v>743</v>
       </c>
     </row>
     <row r="151" spans="1:27">
-      <c r="A151" s="2" t="s">
-        <v>837</v>
+      <c r="A151" s="5" t="s">
+        <v>744</v>
       </c>
       <c r="B151" t="s">
         <v>58</v>
@@ -12251,12 +12497,12 @@
         <v>0</v>
       </c>
       <c r="AA151" t="s">
-        <v>838</v>
+        <v>745</v>
       </c>
     </row>
     <row r="152" spans="1:27">
-      <c r="A152" s="2" t="s">
-        <v>839</v>
+      <c r="A152" s="5" t="s">
+        <v>746</v>
       </c>
       <c r="B152" t="s">
         <v>155</v>
@@ -12268,12 +12514,12 @@
         <v>0</v>
       </c>
       <c r="AA152" t="s">
-        <v>840</v>
+        <v>747</v>
       </c>
     </row>
     <row r="153" spans="1:27">
-      <c r="A153" s="2" t="s">
-        <v>841</v>
+      <c r="A153" s="5" t="s">
+        <v>748</v>
       </c>
       <c r="B153" t="s">
         <v>79</v>
@@ -12285,11 +12531,11 @@
         <v>0</v>
       </c>
       <c r="AA153" t="s">
-        <v>842</v>
+        <v>749</v>
       </c>
     </row>
     <row r="154" spans="1:27">
-      <c r="A154" s="2" t="s">
+      <c r="A154" s="5" t="s">
         <v>113</v>
       </c>
       <c r="B154" t="s">
@@ -12308,37 +12554,37 @@
         <v>1</v>
       </c>
       <c r="H154">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I154">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J154">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K154">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L154">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M154">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N154">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="O154">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="P154">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q154">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R154">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S154">
         <v>4</v>
@@ -12353,13 +12599,13 @@
         <v>0</v>
       </c>
       <c r="W154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X154">
         <v>2</v>
       </c>
       <c r="Y154">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z154">
         <v>152</v>
@@ -12369,143 +12615,143 @@
       </c>
     </row>
     <row r="155" spans="1:27">
-      <c r="A155" s="2" t="s">
+      <c r="A155" s="5" t="s">
         <v>115</v>
       </c>
       <c r="E155">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F155">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G155">
+        <v>47</v>
+      </c>
+      <c r="H155">
+        <v>41</v>
+      </c>
+      <c r="I155">
+        <v>41</v>
+      </c>
+      <c r="J155">
+        <v>45</v>
+      </c>
+      <c r="K155">
+        <v>47</v>
+      </c>
+      <c r="L155">
+        <v>49</v>
+      </c>
+      <c r="M155">
+        <v>45</v>
+      </c>
+      <c r="N155">
+        <v>49</v>
+      </c>
+      <c r="O155">
         <v>48</v>
       </c>
-      <c r="H155">
-        <v>46</v>
-      </c>
-      <c r="I155">
-        <v>42</v>
-      </c>
-      <c r="J155">
-        <v>44</v>
-      </c>
-      <c r="K155">
-        <v>55</v>
-      </c>
-      <c r="L155">
-        <v>66</v>
-      </c>
-      <c r="M155">
-        <v>73</v>
-      </c>
-      <c r="N155">
-        <v>77</v>
-      </c>
-      <c r="O155">
-        <v>67</v>
-      </c>
       <c r="P155">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="Q155">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="R155">
         <v>56</v>
       </c>
       <c r="S155">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="T155">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="U155">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V155">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="W155">
         <v>52</v>
       </c>
       <c r="X155">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="Y155">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="156" spans="1:27">
+      <c r="A156" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E156">
+        <v>32</v>
+      </c>
+      <c r="F156">
+        <v>40</v>
+      </c>
+      <c r="G156">
         <v>39</v>
       </c>
-    </row>
-    <row r="156" spans="1:27">
-      <c r="A156" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E156">
+      <c r="H156">
+        <v>39</v>
+      </c>
+      <c r="I156">
+        <v>36</v>
+      </c>
+      <c r="J156">
+        <v>38</v>
+      </c>
+      <c r="K156">
+        <v>37</v>
+      </c>
+      <c r="L156">
+        <v>35</v>
+      </c>
+      <c r="M156">
         <v>34</v>
       </c>
-      <c r="F156">
-        <v>48</v>
-      </c>
-      <c r="G156">
-        <v>46</v>
-      </c>
-      <c r="H156">
+      <c r="N156">
+        <v>39</v>
+      </c>
+      <c r="O156">
+        <v>42</v>
+      </c>
+      <c r="P156">
+        <v>31</v>
+      </c>
+      <c r="Q156">
+        <v>43</v>
+      </c>
+      <c r="R156">
+        <v>49</v>
+      </c>
+      <c r="S156">
+        <v>40</v>
+      </c>
+      <c r="T156">
+        <v>30</v>
+      </c>
+      <c r="U156">
         <v>41</v>
       </c>
-      <c r="I156">
-        <v>39</v>
-      </c>
-      <c r="J156">
-        <v>35</v>
-      </c>
-      <c r="K156">
+      <c r="V156">
+        <v>42</v>
+      </c>
+      <c r="W156">
         <v>43</v>
       </c>
-      <c r="L156">
-        <v>44</v>
-      </c>
-      <c r="M156">
-        <v>46</v>
-      </c>
-      <c r="N156">
-        <v>44</v>
-      </c>
-      <c r="O156">
-        <v>43</v>
-      </c>
-      <c r="P156">
-        <v>35</v>
-      </c>
-      <c r="Q156">
-        <v>42</v>
-      </c>
-      <c r="R156">
-        <v>45</v>
-      </c>
-      <c r="S156">
-        <v>29</v>
-      </c>
-      <c r="T156">
-        <v>38</v>
-      </c>
-      <c r="U156">
-        <v>43</v>
-      </c>
-      <c r="V156">
-        <v>43</v>
-      </c>
-      <c r="W156">
-        <v>44</v>
-      </c>
       <c r="X156">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="Y156">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="157" spans="1:27">
-      <c r="A157" s="2" t="s">
+      <c r="A157" s="5" t="s">
         <v>117</v>
       </c>
       <c r="E157">
@@ -12515,349 +12761,901 @@
         <v>8</v>
       </c>
       <c r="G157">
+        <v>7</v>
+      </c>
+      <c r="H157">
+        <v>2</v>
+      </c>
+      <c r="I157">
         <v>1</v>
       </c>
-      <c r="H157">
-        <v>3</v>
-      </c>
-      <c r="I157">
-        <v>2</v>
-      </c>
       <c r="J157">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K157">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L157">
+        <v>5</v>
+      </c>
+      <c r="M157">
         <v>4</v>
-      </c>
-      <c r="M157">
-        <v>1</v>
       </c>
       <c r="N157">
         <v>2</v>
       </c>
       <c r="O157">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P157">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q157">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R157">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S157">
+        <v>5</v>
+      </c>
+      <c r="T157">
         <v>3</v>
-      </c>
-      <c r="T157">
-        <v>4</v>
       </c>
       <c r="U157">
         <v>2</v>
       </c>
       <c r="V157">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W157">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X157">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y157">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:27">
-      <c r="A158" s="2" t="s">
+      <c r="A158" s="5" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="159" spans="1:27">
-      <c r="A159" s="2" t="s">
-        <v>126</v>
+      <c r="A159" s="5" t="s">
+        <v>1237</v>
       </c>
       <c r="E159" t="s">
-        <v>843</v>
+        <v>1287</v>
       </c>
       <c r="F159" t="s">
-        <v>844</v>
+        <v>1288</v>
       </c>
       <c r="G159" t="s">
-        <v>845</v>
+        <v>1289</v>
       </c>
       <c r="H159" t="s">
-        <v>846</v>
+        <v>1290</v>
       </c>
       <c r="I159" t="s">
-        <v>847</v>
+        <v>1291</v>
       </c>
       <c r="J159" t="s">
-        <v>848</v>
+        <v>1292</v>
       </c>
       <c r="K159" t="s">
-        <v>849</v>
+        <v>1293</v>
       </c>
       <c r="L159" t="s">
-        <v>850</v>
+        <v>1294</v>
       </c>
       <c r="M159" t="s">
-        <v>851</v>
+        <v>1295</v>
       </c>
       <c r="N159" t="s">
-        <v>852</v>
+        <v>1296</v>
       </c>
       <c r="O159" t="s">
-        <v>853</v>
+        <v>1297</v>
       </c>
       <c r="P159" t="s">
-        <v>854</v>
+        <v>1298</v>
       </c>
       <c r="Q159" t="s">
-        <v>855</v>
+        <v>1299</v>
       </c>
       <c r="R159" t="s">
-        <v>856</v>
+        <v>1300</v>
       </c>
       <c r="S159" t="s">
-        <v>857</v>
+        <v>1301</v>
       </c>
       <c r="T159" t="s">
-        <v>858</v>
+        <v>1302</v>
       </c>
       <c r="U159" t="s">
-        <v>859</v>
+        <v>1303</v>
       </c>
       <c r="V159" t="s">
-        <v>860</v>
+        <v>1304</v>
       </c>
       <c r="W159" t="s">
-        <v>861</v>
+        <v>1305</v>
       </c>
       <c r="X159" t="s">
-        <v>862</v>
+        <v>1306</v>
       </c>
       <c r="Y159" t="s">
-        <v>863</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="160" spans="1:27">
-      <c r="A160" s="2" t="s">
-        <v>130</v>
+      <c r="A160" s="5" t="s">
+        <v>1236</v>
       </c>
       <c r="E160" t="s">
-        <v>864</v>
+        <v>1308</v>
       </c>
       <c r="F160" t="s">
-        <v>865</v>
+        <v>1309</v>
       </c>
       <c r="G160" t="s">
-        <v>866</v>
+        <v>1310</v>
       </c>
       <c r="H160" t="s">
-        <v>867</v>
+        <v>1311</v>
       </c>
       <c r="I160" t="s">
-        <v>868</v>
+        <v>1312</v>
       </c>
       <c r="J160" t="s">
-        <v>869</v>
+        <v>1313</v>
       </c>
       <c r="K160" t="s">
-        <v>870</v>
+        <v>1314</v>
       </c>
       <c r="L160" t="s">
-        <v>871</v>
+        <v>1315</v>
       </c>
       <c r="M160" t="s">
-        <v>872</v>
+        <v>1316</v>
       </c>
       <c r="N160" t="s">
-        <v>873</v>
+        <v>1317</v>
       </c>
       <c r="O160" t="s">
-        <v>874</v>
+        <v>1318</v>
       </c>
       <c r="P160" t="s">
-        <v>875</v>
+        <v>1319</v>
       </c>
       <c r="Q160" t="s">
-        <v>876</v>
+        <v>1320</v>
       </c>
       <c r="R160" t="s">
-        <v>877</v>
+        <v>1321</v>
       </c>
       <c r="S160" t="s">
-        <v>878</v>
+        <v>1322</v>
       </c>
       <c r="T160" t="s">
-        <v>879</v>
+        <v>1323</v>
       </c>
       <c r="U160" t="s">
-        <v>880</v>
+        <v>1324</v>
       </c>
       <c r="V160" t="s">
-        <v>881</v>
+        <v>1325</v>
       </c>
       <c r="W160" t="s">
-        <v>882</v>
+        <v>1326</v>
       </c>
       <c r="X160" t="s">
-        <v>883</v>
+        <v>1327</v>
       </c>
       <c r="Y160" t="s">
-        <v>884</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="161" spans="1:27">
-      <c r="A161" s="2" t="s">
-        <v>134</v>
+      <c r="A161" s="5" t="s">
+        <v>1235</v>
       </c>
       <c r="E161" t="s">
-        <v>885</v>
+        <v>1329</v>
       </c>
       <c r="F161" t="s">
-        <v>886</v>
+        <v>1330</v>
       </c>
       <c r="G161" t="s">
-        <v>887</v>
+        <v>1331</v>
       </c>
       <c r="H161" t="s">
-        <v>888</v>
+        <v>1332</v>
       </c>
       <c r="I161" t="s">
-        <v>889</v>
+        <v>1333</v>
       </c>
       <c r="J161" t="s">
-        <v>890</v>
+        <v>1334</v>
       </c>
       <c r="K161" t="s">
-        <v>891</v>
+        <v>1335</v>
       </c>
       <c r="L161" t="s">
-        <v>892</v>
+        <v>1336</v>
       </c>
       <c r="M161" t="s">
-        <v>893</v>
+        <v>1337</v>
       </c>
       <c r="N161" t="s">
-        <v>894</v>
+        <v>1338</v>
       </c>
       <c r="O161" t="s">
-        <v>895</v>
+        <v>1339</v>
       </c>
       <c r="P161" t="s">
-        <v>896</v>
+        <v>1340</v>
       </c>
       <c r="Q161" t="s">
-        <v>897</v>
+        <v>1341</v>
       </c>
       <c r="R161" t="s">
-        <v>898</v>
+        <v>1342</v>
       </c>
       <c r="S161" t="s">
-        <v>899</v>
+        <v>1343</v>
       </c>
       <c r="T161" t="s">
-        <v>900</v>
+        <v>1344</v>
       </c>
       <c r="U161" t="s">
-        <v>901</v>
+        <v>1345</v>
       </c>
       <c r="V161" t="s">
-        <v>902</v>
+        <v>1346</v>
       </c>
       <c r="W161" t="s">
-        <v>903</v>
+        <v>1347</v>
       </c>
       <c r="X161" t="s">
-        <v>904</v>
+        <v>1348</v>
       </c>
       <c r="Y161" t="s">
-        <v>905</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="162" spans="1:27">
-      <c r="A162" s="2" t="s">
+      <c r="A162" s="5" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E162" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F162" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G162" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H162" t="s">
+        <v>1230</v>
+      </c>
+      <c r="I162" t="s">
+        <v>1229</v>
+      </c>
+      <c r="J162" t="s">
+        <v>1228</v>
+      </c>
+      <c r="K162" t="s">
+        <v>1227</v>
+      </c>
+      <c r="L162" t="s">
+        <v>1226</v>
+      </c>
+      <c r="M162" t="s">
+        <v>1225</v>
+      </c>
+      <c r="N162" t="s">
+        <v>1224</v>
+      </c>
+      <c r="O162" t="s">
+        <v>1223</v>
+      </c>
+      <c r="P162" t="s">
+        <v>1222</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>1221</v>
+      </c>
+      <c r="R162" t="s">
+        <v>1220</v>
+      </c>
+      <c r="S162" t="s">
+        <v>1219</v>
+      </c>
+      <c r="T162" t="s">
+        <v>1218</v>
+      </c>
+      <c r="U162" t="s">
+        <v>1217</v>
+      </c>
+      <c r="V162" t="s">
+        <v>1216</v>
+      </c>
+      <c r="W162" t="s">
+        <v>1215</v>
+      </c>
+      <c r="X162" t="s">
+        <v>1214</v>
+      </c>
+      <c r="Y162" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="163" spans="1:27">
+      <c r="A163" s="5" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E163" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F163" t="s">
+        <v>1210</v>
+      </c>
+      <c r="G163" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H163" t="s">
+        <v>1208</v>
+      </c>
+      <c r="I163" t="s">
+        <v>1207</v>
+      </c>
+      <c r="J163" t="s">
+        <v>1206</v>
+      </c>
+      <c r="K163" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L163" t="s">
+        <v>1204</v>
+      </c>
+      <c r="M163" t="s">
+        <v>1203</v>
+      </c>
+      <c r="N163" t="s">
+        <v>1202</v>
+      </c>
+      <c r="O163" t="s">
+        <v>1201</v>
+      </c>
+      <c r="P163" t="s">
+        <v>1200</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>1199</v>
+      </c>
+      <c r="R163" t="s">
+        <v>1198</v>
+      </c>
+      <c r="S163" t="s">
+        <v>1197</v>
+      </c>
+      <c r="T163" t="s">
+        <v>1196</v>
+      </c>
+      <c r="U163" t="s">
+        <v>1195</v>
+      </c>
+      <c r="V163" t="s">
+        <v>1194</v>
+      </c>
+      <c r="W163" t="s">
+        <v>1193</v>
+      </c>
+      <c r="X163" t="s">
+        <v>1192</v>
+      </c>
+      <c r="Y163" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="164" spans="1:27">
+      <c r="A164" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E164" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F164" t="s">
+        <v>1188</v>
+      </c>
+      <c r="G164" t="s">
+        <v>1187</v>
+      </c>
+      <c r="H164" t="s">
+        <v>1186</v>
+      </c>
+      <c r="I164" t="s">
+        <v>1185</v>
+      </c>
+      <c r="J164" t="s">
+        <v>1184</v>
+      </c>
+      <c r="K164" t="s">
+        <v>1183</v>
+      </c>
+      <c r="L164" t="s">
+        <v>1182</v>
+      </c>
+      <c r="M164" t="s">
+        <v>1181</v>
+      </c>
+      <c r="N164" t="s">
+        <v>1180</v>
+      </c>
+      <c r="O164" t="s">
+        <v>1179</v>
+      </c>
+      <c r="P164" t="s">
+        <v>1178</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>1177</v>
+      </c>
+      <c r="R164" t="s">
+        <v>1176</v>
+      </c>
+      <c r="S164" t="s">
+        <v>1175</v>
+      </c>
+      <c r="T164" t="s">
+        <v>1174</v>
+      </c>
+      <c r="U164" t="s">
+        <v>1173</v>
+      </c>
+      <c r="V164" t="s">
+        <v>1172</v>
+      </c>
+      <c r="W164" t="s">
+        <v>1171</v>
+      </c>
+      <c r="X164" t="s">
+        <v>1170</v>
+      </c>
+      <c r="Y164" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="165" spans="1:27">
+      <c r="A165" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F165" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G165" t="s">
+        <v>1166</v>
+      </c>
+      <c r="H165" t="s">
+        <v>1165</v>
+      </c>
+      <c r="I165" t="s">
+        <v>1164</v>
+      </c>
+      <c r="J165" t="s">
+        <v>1163</v>
+      </c>
+      <c r="K165" t="s">
+        <v>1162</v>
+      </c>
+      <c r="L165" t="s">
+        <v>1161</v>
+      </c>
+      <c r="M165" t="s">
+        <v>1160</v>
+      </c>
+      <c r="N165" t="s">
+        <v>1159</v>
+      </c>
+      <c r="O165" t="s">
+        <v>1158</v>
+      </c>
+      <c r="P165" t="s">
+        <v>1157</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>1156</v>
+      </c>
+      <c r="R165" t="s">
+        <v>1155</v>
+      </c>
+      <c r="S165" t="s">
+        <v>1154</v>
+      </c>
+      <c r="T165" t="s">
+        <v>1153</v>
+      </c>
+      <c r="U165" t="s">
+        <v>1152</v>
+      </c>
+      <c r="V165" t="s">
+        <v>1151</v>
+      </c>
+      <c r="W165" t="s">
+        <v>1150</v>
+      </c>
+      <c r="X165" t="s">
+        <v>1149</v>
+      </c>
+      <c r="Y165" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="166" spans="1:27">
+      <c r="A166" s="5" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F166" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G166" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H166" t="s">
+        <v>1144</v>
+      </c>
+      <c r="J166" t="s">
+        <v>1143</v>
+      </c>
+      <c r="K166" t="s">
+        <v>1142</v>
+      </c>
+      <c r="L166" t="s">
+        <v>1141</v>
+      </c>
+      <c r="M166" t="s">
+        <v>1140</v>
+      </c>
+      <c r="N166" t="s">
+        <v>1139</v>
+      </c>
+      <c r="O166" t="s">
+        <v>1138</v>
+      </c>
+      <c r="P166" t="s">
+        <v>1137</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>1136</v>
+      </c>
+      <c r="R166" t="s">
+        <v>1135</v>
+      </c>
+      <c r="S166" t="s">
+        <v>1134</v>
+      </c>
+      <c r="T166" t="s">
+        <v>1133</v>
+      </c>
+      <c r="U166" t="s">
+        <v>1132</v>
+      </c>
+      <c r="V166" t="s">
+        <v>1131</v>
+      </c>
+      <c r="W166" t="s">
+        <v>1130</v>
+      </c>
+      <c r="Y166" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="167" spans="1:27">
+      <c r="A167" s="5" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F167" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G167" t="s">
+        <v>1126</v>
+      </c>
+      <c r="J167" t="s">
+        <v>1125</v>
+      </c>
+      <c r="K167" t="s">
+        <v>1124</v>
+      </c>
+      <c r="L167" t="s">
+        <v>1123</v>
+      </c>
+      <c r="M167" t="s">
+        <v>1122</v>
+      </c>
+      <c r="O167" t="s">
+        <v>1121</v>
+      </c>
+      <c r="P167" t="s">
+        <v>1120</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>1119</v>
+      </c>
+      <c r="R167" t="s">
+        <v>1118</v>
+      </c>
+      <c r="S167" t="s">
+        <v>1117</v>
+      </c>
+      <c r="T167" t="s">
+        <v>1116</v>
+      </c>
+      <c r="V167" t="s">
+        <v>1115</v>
+      </c>
+      <c r="W167" t="s">
+        <v>1114</v>
+      </c>
+      <c r="Y167" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="168" spans="1:27">
+      <c r="A168" s="5" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F168" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G168" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H168" t="s">
+        <v>1109</v>
+      </c>
+      <c r="I168" t="s">
+        <v>1108</v>
+      </c>
+      <c r="J168" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K168" t="s">
+        <v>1106</v>
+      </c>
+      <c r="L168" t="s">
+        <v>1105</v>
+      </c>
+      <c r="M168" t="s">
+        <v>1104</v>
+      </c>
+      <c r="N168" t="s">
+        <v>1103</v>
+      </c>
+      <c r="O168" t="s">
+        <v>1102</v>
+      </c>
+      <c r="P168" t="s">
+        <v>1101</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>1100</v>
+      </c>
+      <c r="R168" t="s">
+        <v>1099</v>
+      </c>
+      <c r="S168" t="s">
+        <v>1098</v>
+      </c>
+      <c r="T168" t="s">
+        <v>1097</v>
+      </c>
+      <c r="U168" t="s">
+        <v>1096</v>
+      </c>
+      <c r="V168" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W168" t="s">
+        <v>1075</v>
+      </c>
+      <c r="X168" t="s">
+        <v>1094</v>
+      </c>
+      <c r="Y168" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="169" spans="1:27">
+      <c r="A169" s="5" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F169" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G169" t="s">
+        <v>1090</v>
+      </c>
+      <c r="H169" t="s">
+        <v>1089</v>
+      </c>
+      <c r="J169" t="s">
+        <v>1088</v>
+      </c>
+      <c r="K169" t="s">
+        <v>1087</v>
+      </c>
+      <c r="L169" t="s">
+        <v>1086</v>
+      </c>
+      <c r="M169" t="s">
+        <v>1085</v>
+      </c>
+      <c r="N169" t="s">
+        <v>1084</v>
+      </c>
+      <c r="O169" t="s">
+        <v>1083</v>
+      </c>
+      <c r="P169" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>1081</v>
+      </c>
+      <c r="R169" t="s">
+        <v>1080</v>
+      </c>
+      <c r="S169" t="s">
+        <v>1079</v>
+      </c>
+      <c r="T169" t="s">
+        <v>1078</v>
+      </c>
+      <c r="U169" t="s">
+        <v>1077</v>
+      </c>
+      <c r="V169" t="s">
+        <v>1076</v>
+      </c>
+      <c r="W169" t="s">
+        <v>1075</v>
+      </c>
+      <c r="Y169" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="170" spans="1:27">
+      <c r="A170" s="5" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F170" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G170" t="s">
+        <v>1071</v>
+      </c>
+      <c r="J170" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K170" t="s">
+        <v>1069</v>
+      </c>
+      <c r="L170" t="s">
+        <v>1068</v>
+      </c>
+      <c r="M170" t="s">
+        <v>1067</v>
+      </c>
+      <c r="O170" t="s">
+        <v>1066</v>
+      </c>
+      <c r="P170" t="s">
+        <v>1065</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>1064</v>
+      </c>
+      <c r="R170" t="s">
+        <v>1063</v>
+      </c>
+      <c r="S170" t="s">
+        <v>1062</v>
+      </c>
+      <c r="T170" t="s">
+        <v>1061</v>
+      </c>
+      <c r="V170" t="s">
+        <v>1060</v>
+      </c>
+      <c r="W170" t="s">
+        <v>1059</v>
+      </c>
+      <c r="Y170" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="171" spans="1:27">
+      <c r="A171" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B162">
-        <v>0</v>
-      </c>
-      <c r="C162">
-        <v>0</v>
-      </c>
-      <c r="E162">
-        <v>0</v>
-      </c>
-      <c r="F162">
-        <v>0</v>
-      </c>
-      <c r="G162">
-        <v>0</v>
-      </c>
-      <c r="H162">
-        <v>0</v>
-      </c>
-      <c r="I162">
-        <v>0</v>
-      </c>
-      <c r="J162">
-        <v>0</v>
-      </c>
-      <c r="K162">
-        <v>0</v>
-      </c>
-      <c r="L162">
-        <v>0</v>
-      </c>
-      <c r="M162">
-        <v>0</v>
-      </c>
-      <c r="N162">
-        <v>0</v>
-      </c>
-      <c r="O162">
-        <v>0</v>
-      </c>
-      <c r="P162">
-        <v>0</v>
-      </c>
-      <c r="Q162">
-        <v>0</v>
-      </c>
-      <c r="R162">
-        <v>0</v>
-      </c>
-      <c r="S162">
-        <v>0</v>
-      </c>
-      <c r="T162">
-        <v>0</v>
-      </c>
-      <c r="U162">
-        <v>0</v>
-      </c>
-      <c r="V162">
-        <v>0</v>
-      </c>
-      <c r="W162">
-        <v>0</v>
-      </c>
-      <c r="X162">
-        <v>0</v>
-      </c>
-      <c r="Y162">
-        <v>0</v>
-      </c>
-      <c r="Z162">
-        <v>0</v>
-      </c>
-      <c r="AA162">
+      <c r="B171">
+        <v>0</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+      <c r="E171">
+        <v>0</v>
+      </c>
+      <c r="F171">
+        <v>0</v>
+      </c>
+      <c r="G171">
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <v>0</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+      <c r="M171">
+        <v>0</v>
+      </c>
+      <c r="N171">
+        <v>0</v>
+      </c>
+      <c r="O171">
+        <v>0</v>
+      </c>
+      <c r="P171">
+        <v>0</v>
+      </c>
+      <c r="Q171">
+        <v>0</v>
+      </c>
+      <c r="R171">
+        <v>0</v>
+      </c>
+      <c r="S171">
+        <v>0</v>
+      </c>
+      <c r="T171">
+        <v>0</v>
+      </c>
+      <c r="U171">
+        <v>0</v>
+      </c>
+      <c r="V171">
+        <v>0</v>
+      </c>
+      <c r="W171">
+        <v>0</v>
+      </c>
+      <c r="X171">
+        <v>0</v>
+      </c>
+      <c r="Y171">
+        <v>0</v>
+      </c>
+      <c r="Z171">
+        <v>0</v>
+      </c>
+      <c r="AA171">
         <v>0</v>
       </c>
     </row>
